--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -207,7 +207,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -895,7 +897,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!$B$4&amp;" · Andamento dos processos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
         <v/>
@@ -2303,12 +2305,13 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
@@ -2367,7 +2370,7 @@
     <col width="4" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações</t>
@@ -2571,8 +2574,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2603,7 +2607,7 @@
     <col hidden="1" width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Processos</t>
@@ -13117,8 +13121,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:M304"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:M304">
     <cfRule type="expression" priority="1" dxfId="1">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela "Parados" ou "Por responsável" e use o prompt "Carteira 03: resumo da situação dos casos para a reunião de sócios" da biblioteca do kit.</t>
+          <t>Copie a tabela "Parados" ou "Por responsável" e use o prompt "Prazos 05 · Resumo de andamento para o sócio" da biblioteca do kit.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Processos, apague os exemplos e cadastre os seus casos: número, cliente, área, fase, responsável, próxima ação com data, e a data da última atualização.</t>
+          <t>Em Processos, apague os exemplos e cadastre os seus casos: número, cliente, área, fase, responsável, próxima ação com data, e a data da última atualização. O cadastro (número, cliente, área, fase, responsável) é o mesmo da planilha 13 · Carteira: copie de lá e mantenha a 13 como fonte.</t>
         </is>
       </c>
     </row>
@@ -787,82 +787,94 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Com a IA</t>
+          <t>Exemplo</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela "Parados" ou "Por responsável" e use o prompt "Prazos 05 · Resumo de andamento para o sócio" da biblioteca do kit.</t>
+          <t>Caso consultivo não tem número de processo (referência CONS-ano-nº) e a próxima ação é entrega de parecer ou reunião. A próxima ação de cada caso é coerente com a fase (inicial: contestação, réplica, juntada, conciliação; instrução: audiência, laudo, alegações finais; sentença: embargos, recurso; recurso: contrarrazões; execução: cumprimento, penhora; acordo: minuta, homologação).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Com a IA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
+          <t>Copie a tabela "Parados" ou "Por responsável" e use o prompt "Prazos 05 · Resumo de andamento para o sócio" da biblioteca do kit.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -898,9 +910,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Andamento dos processos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Andamento dos processos · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -935,9 +947,9 @@
         </is>
       </c>
       <c r="H4" s="14" t="n"/>
-      <c r="I4" s="9">
+      <c r="I4" s="9" t="str">
         <f>"Parados há mais de "&amp;Config!$B$6&amp;" dias"</f>
-        <v/>
+        <v>Parados há mais de 30 dias</v>
       </c>
       <c r="J4" s="10" t="n"/>
       <c r="K4" s="15" t="inlineStr">
@@ -950,32 +962,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="17">
         <f>COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,"&lt;&gt;Encerrado")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="18">
         <f>COUNTIFS(Processos!$K$5:$K$304,"Atrasado")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="19">
         <f>COUNTIFS(Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$K$5:$K$304,"Esta semana")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="20">
         <f>COUNTIFS(Processos!$K$5:$K$304,"Sem próxima ação")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="18">
         <f>COUNTIFS(Processos!$M$5:$M$304,"Sim")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="21">
         <f>COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,"Encerrado")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="L5" s="16" t="n"/>
     </row>
@@ -1049,259 +1061,259 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="24" t="str">
         <f>IF(Config!$B$10="","",Config!$B$10)</f>
-        <v/>
+        <v>Consultivo</v>
       </c>
       <c r="B9" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$10))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C9" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$10,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D9" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$10,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$10,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E9" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$10,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F9" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$10,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
-      </c>
-      <c r="H9" s="24">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="str">
         <f>IF(Config!$D$10="","",Config!$D$10)</f>
-        <v/>
+        <v>Cível</v>
       </c>
       <c r="I9" s="25">
         <f>IF(Config!$D$10="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$C$5:$C$304,Config!$D$10,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="J9" s="25">
         <f>IF(Config!$D$10="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$10,Processos!$D$5:$D$304,"Encerrado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K9" s="25">
         <f>IF(Config!$D$10="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$10,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="L9" s="25">
         <f>IF(Config!$D$10="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$10,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24">
+      <c r="A10" s="24" t="str">
         <f>IF(Config!$B$11="","",Config!$B$11)</f>
-        <v/>
+        <v>Inicial</v>
       </c>
       <c r="B10" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$11))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C10" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$11,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D10" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$11,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$11,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E10" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$11,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F10" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$11,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
-      </c>
-      <c r="H10" s="24">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="str">
         <f>IF(Config!$D$11="","",Config!$D$11)</f>
-        <v/>
+        <v>Trabalhista</v>
       </c>
       <c r="I10" s="25">
         <f>IF(Config!$D$11="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$C$5:$C$304,Config!$D$11,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="J10" s="25">
         <f>IF(Config!$D$11="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$11,Processos!$D$5:$D$304,"Encerrado"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K10" s="25">
         <f>IF(Config!$D$11="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$11,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L10" s="25">
         <f>IF(Config!$D$11="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$11,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="24" t="str">
         <f>IF(Config!$B$12="","",Config!$B$12)</f>
-        <v/>
+        <v>Instrução</v>
       </c>
       <c r="B11" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$12))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C11" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$12,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D11" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$12,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$12,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E11" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$12,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F11" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$12,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
-      </c>
-      <c r="H11" s="24">
+        <v>0</v>
+      </c>
+      <c r="H11" s="24" t="str">
         <f>IF(Config!$D$12="","",Config!$D$12)</f>
-        <v/>
+        <v>Previdenciário</v>
       </c>
       <c r="I11" s="25">
         <f>IF(Config!$D$12="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$C$5:$C$304,Config!$D$12,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J11" s="25">
         <f>IF(Config!$D$12="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$12,Processos!$D$5:$D$304,"Encerrado"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K11" s="25">
         <f>IF(Config!$D$12="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$12,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="L11" s="25">
         <f>IF(Config!$D$12="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$12,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24">
+      <c r="A12" s="24" t="str">
         <f>IF(Config!$B$13="","",Config!$B$13)</f>
-        <v/>
+        <v>Sentença</v>
       </c>
       <c r="B12" s="25">
         <f>IF(Config!$B$13="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$13))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C12" s="25">
         <f>IF(Config!$B$13="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$13,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D12" s="25">
         <f>IF(Config!$B$13="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$13,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$13,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E12" s="25">
         <f>IF(Config!$B$13="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$13,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F12" s="25">
         <f>IF(Config!$B$13="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$13,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
-      </c>
-      <c r="H12" s="24">
+        <v>0</v>
+      </c>
+      <c r="H12" s="24" t="str">
         <f>IF(Config!$D$13="","",Config!$D$13)</f>
-        <v/>
+        <v>Empresarial</v>
       </c>
       <c r="I12" s="25">
         <f>IF(Config!$D$13="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$C$5:$C$304,Config!$D$13,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="J12" s="25">
         <f>IF(Config!$D$13="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$13,Processos!$D$5:$D$304,"Encerrado"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K12" s="25">
         <f>IF(Config!$D$13="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$13,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L12" s="25">
         <f>IF(Config!$D$13="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$13,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24">
+      <c r="A13" s="24" t="str">
         <f>IF(Config!$B$14="","",Config!$B$14)</f>
-        <v/>
+        <v>Recurso</v>
       </c>
       <c r="B13" s="25">
         <f>IF(Config!$B$14="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$14))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C13" s="25">
         <f>IF(Config!$B$14="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$14,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D13" s="25">
         <f>IF(Config!$B$14="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$14,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$14,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E13" s="25">
         <f>IF(Config!$B$14="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$14,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F13" s="25">
         <f>IF(Config!$B$14="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$14,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="24">
+        <v>0</v>
+      </c>
+      <c r="H13" s="24" t="str">
         <f>IF(Config!$D$14="","",Config!$D$14)</f>
-        <v/>
+        <v>Família</v>
       </c>
       <c r="I13" s="25">
         <f>IF(Config!$D$14="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$C$5:$C$304,Config!$D$14,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J13" s="25">
         <f>IF(Config!$D$14="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$14,Processos!$D$5:$D$304,"Encerrado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K13" s="25">
         <f>IF(Config!$D$14="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$14,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L13" s="25">
         <f>IF(Config!$D$14="","",COUNTIFS(Processos!$C$5:$C$304,Config!$D$14,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24">
+      <c r="A14" s="24" t="str">
         <f>IF(Config!$B$15="","",Config!$B$15)</f>
-        <v/>
+        <v>Execução</v>
       </c>
       <c r="B14" s="25">
         <f>IF(Config!$B$15="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$15))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C14" s="25">
         <f>IF(Config!$B$15="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$15,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D14" s="25">
         <f>IF(Config!$B$15="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$15,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$15,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E14" s="25">
         <f>IF(Config!$B$15="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$15,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F14" s="25">
         <f>IF(Config!$B$15="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$15,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H14" s="24">
         <f>IF(Config!$D$15="","",Config!$D$15)</f>
@@ -1325,29 +1337,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24">
+      <c r="A15" s="24" t="str">
         <f>IF(Config!$B$16="","",Config!$B$16)</f>
-        <v/>
+        <v>Acordo</v>
       </c>
       <c r="B15" s="25">
         <f>IF(Config!$B$16="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$16))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C15" s="25">
         <f>IF(Config!$B$16="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$16,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D15" s="25">
         <f>IF(Config!$B$16="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$16,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$16,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E15" s="25">
         <f>IF(Config!$B$16="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$16,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F15" s="25">
         <f>IF(Config!$B$16="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$16,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H15" s="24">
         <f>IF(Config!$D$16="","",Config!$D$16)</f>
@@ -1371,29 +1383,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="24" t="str">
         <f>IF(Config!$B$17="","",Config!$B$17)</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="B16" s="25">
         <f>IF(Config!$B$17="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$D$5:$D$304,Config!$B$17))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C16" s="25">
         <f>IF(Config!$B$17="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$17,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D16" s="25">
         <f>IF(Config!$B$17="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$17,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$D$5:$D$304,Config!$B$17,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E16" s="25">
         <f>IF(Config!$B$17="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$17,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F16" s="25">
         <f>IF(Config!$B$17="","",COUNTIFS(Processos!$D$5:$D$304,Config!$B$17,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H16" s="24">
         <f>IF(Config!$D$17="","",Config!$D$17)</f>
@@ -1548,97 +1560,97 @@
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Ação mais próxima</t>
+          <t>Próxima ação a partir de hoje</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24">
+      <c r="A23" s="24" t="str">
         <f>IF(Config!$F$10="","",Config!$F$10)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="B23" s="25">
         <f>IF(Config!$F$10="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$E$5:$E$304,Config!$F$10,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C23" s="25">
         <f>IF(Config!$F$10="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$10,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D23" s="25">
         <f>IF(Config!$F$10="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$10,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$E$5:$E$304,Config!$F$10,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="E23" s="25">
         <f>IF(Config!$F$10="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$10,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F23" s="25">
         <f>IF(Config!$F$10="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$10,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G23" s="26">
-        <f>IF(Config!$F$10="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$10,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$10,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
-        <v/>
+        <f>IF(Config!$F$10="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$10)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$10)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$10)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$10)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24">
+      <c r="A24" s="24" t="str">
         <f>IF(Config!$F$11="","",Config!$F$11)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="B24" s="25">
         <f>IF(Config!$F$11="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$E$5:$E$304,Config!$F$11,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C24" s="25">
         <f>IF(Config!$F$11="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$11,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D24" s="25">
         <f>IF(Config!$F$11="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$11,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$E$5:$E$304,Config!$F$11,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="E24" s="25">
         <f>IF(Config!$F$11="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$11,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F24" s="25">
         <f>IF(Config!$F$11="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$11,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G24" s="26">
-        <f>IF(Config!$F$11="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$11,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$11,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
-        <v/>
+        <f>IF(Config!$F$11="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$11)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$11)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$11)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$11)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24">
+      <c r="A25" s="24" t="str">
         <f>IF(Config!$F$12="","",Config!$F$12)</f>
-        <v/>
+        <v>Júlia Prado</v>
       </c>
       <c r="B25" s="25">
         <f>IF(Config!$F$12="","",COUNTIFS(Processos!$A$5:$A$304,"&lt;&gt;",Processos!$E$5:$E$304,Config!$F$12,Processos!$D$5:$D$304,"&lt;&gt;Encerrado"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C25" s="25">
         <f>IF(Config!$F$12="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$12,Processos!$K$5:$K$304,"Atrasado"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D25" s="25">
         <f>IF(Config!$F$12="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$12,Processos!$K$5:$K$304,"Hoje")+COUNTIFS(Processos!$E$5:$E$304,Config!$F$12,Processos!$K$5:$K$304,"Esta semana"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E25" s="25">
         <f>IF(Config!$F$12="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$12,Processos!$K$5:$K$304,"Sem próxima ação"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F25" s="25">
         <f>IF(Config!$F$12="","",COUNTIFS(Processos!$E$5:$E$304,Config!$F$12,Processos!$M$5:$M$304,"Sim"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G25" s="26">
-        <f>IF(Config!$F$12="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$12,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$12,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$12="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$12)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$12)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$12)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$12)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1668,7 +1680,7 @@
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IF(Config!$F$13="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$13,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$13,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$13="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$13)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$13)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$13)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$13)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1698,7 +1710,7 @@
         <v/>
       </c>
       <c r="G27" s="26">
-        <f>IF(Config!$F$14="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$14,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$14,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$14="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$14)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$14)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$14)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$14)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1728,7 +1740,7 @@
         <v/>
       </c>
       <c r="G28" s="26">
-        <f>IF(Config!$F$15="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$15,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$15,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$15="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$15)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$15)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$15)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$15)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1758,7 +1770,7 @@
         <v/>
       </c>
       <c r="G29" s="26">
-        <f>IF(Config!$F$16="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$16,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$16,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$16="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$16)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$16)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$16)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$16)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1788,7 +1800,7 @@
         <v/>
       </c>
       <c r="G30" s="26">
-        <f>IF(Config!$F$17="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$17,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$17,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$17="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$17)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$17)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$17)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$17)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1818,7 +1830,7 @@
         <v/>
       </c>
       <c r="G31" s="26">
-        <f>IF(Config!$F$18="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$18,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$18,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
+        <f>IF(Config!$F$18="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$18)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$18)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$18)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$18)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
         <v/>
       </c>
     </row>
@@ -1848,14 +1860,21 @@
         <v/>
       </c>
       <c r="G32" s="26">
-        <f>IF(Config!$F$19="","",IFERROR(IF(_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$19,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")=0,"",_xlfn.MINIFS(Processos!$G$5:$G$304,Processos!$E$5:$E$304,Config!$F$19,Processos!$D$5:$D$304,"&lt;&gt;Encerrado",Processos!$G$5:$G$304,"&gt;0")),""))</f>
-        <v/>
+        <f>IF(Config!$F$19="","",IFERROR(IF(SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$19)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$19)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Processos!$E$5:$E$304=Config!$F$19)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5))*Processos!$G$5:$G$304+(1-((Processos!$E$5:$E$304=Config!$F$19)*(Processos!$D$5:$D$304&lt;&gt;"Encerrado")*(Processos!$G$5:$G$304&gt;=Config!$B$5)))*1E+10))),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>Próxima ação a partir de hoje: a data mais próxima entre as ações de hoje em diante; as atrasadas estão na coluna "Ação atrasada".</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22">
+      <c r="A35" s="22" t="str">
         <f>"Parados há mais de "&amp;Config!$B$6&amp;" dias (os mais antigos primeiro)"</f>
-        <v/>
+        <v>Parados há mais de 30 dias (os mais antigos primeiro)</v>
       </c>
     </row>
     <row r="36">
@@ -1911,132 +1930,132 @@
       <c r="A38" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="24">
+        <v>9495290-86.2025.8.26.0503</v>
+      </c>
+      <c r="C38" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="25">
+        <v>Helena Duarte</v>
+      </c>
+      <c r="D38" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="25">
+        <v>Execução</v>
+      </c>
+      <c r="E38" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="F38" s="26">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>46232.0</v>
       </c>
       <c r="G38" s="28">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="24">
+        <v>47</v>
+      </c>
+      <c r="H38" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,1)&gt;0,IF(INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,1),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Iniciar o cumprimento de sentença</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="24">
+        <v>9236009-85.2025.8.26.0452</v>
+      </c>
+      <c r="C39" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="25">
+        <v>Bistrô 42</v>
+      </c>
+      <c r="D39" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="25">
+        <v>Execução</v>
+      </c>
+      <c r="E39" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="F39" s="26">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>46238.0</v>
       </c>
       <c r="G39" s="28">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="24">
+        <v>41</v>
+      </c>
+      <c r="H39" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,2)&gt;0,IF(INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,2),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Iniciar o cumprimento de sentença</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="24">
+        <v>6184138-13.2026.8.26.0378</v>
+      </c>
+      <c r="C40" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="25">
+        <v>Oficina Mecânica Central</v>
+      </c>
+      <c r="D40" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="25">
+        <v>Inicial</v>
+      </c>
+      <c r="E40" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="F40" s="26">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>46243.0</v>
       </c>
       <c r="G40" s="28">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="24">
+        <v>36</v>
+      </c>
+      <c r="H40" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,3)&gt;0,IF(INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,3),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Audiência de conciliação (confirmar presença do cliente)</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$A$5:$A$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="24">
+        <v>2521428-61.2026.8.26.0600</v>
+      </c>
+      <c r="C41" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$B$5:$B$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="25">
+        <v>Luciana Farias</v>
+      </c>
+      <c r="D41" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$D$5:$D$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="25">
+        <v>Acordo</v>
+      </c>
+      <c r="E41" s="25" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$E$5:$E$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="F41" s="26">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$H$5:$H$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>46246.0</v>
       </c>
       <c r="G41" s="28">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$L$5:$L$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="24">
+        <v>33</v>
+      </c>
+      <c r="H41" s="24" t="str">
         <f>IFERROR(IF(LARGE(Processos!$N$5:$N$304,4)&gt;0,IF(INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))="","",INDEX(Processos!$F$5:$F$304,MATCH(LARGE(Processos!$N$5:$N$304,4),Processos!$N$5:$N$304,0))),""),"")</f>
-        <v/>
+        <v>Acompanhar a homologação do acordo</v>
       </c>
     </row>
     <row r="42">
@@ -2404,7 +2423,7 @@
       </c>
       <c r="B5" s="31">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
@@ -2617,7 +2636,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Uma linha por caso. Preencha as colunas amarelas; dias, situação e parado são calculados. A cada movimentação, atualize a fase, a próxima ação e a data da última atualização.</t>
+          <t>Uma linha por caso (copie o cadastro da planilha 13 · Carteira, aba Casos: a 13 é a fonte). Preencha as colunas amarelas; dias, situação e parado são calculados. A cada movimentação, atualize a fase, a próxima ação e a data da última atualização.</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2715,7 @@
     <row r="5">
       <c r="A5" s="30" t="inlineStr">
         <is>
-          <t>9236009-85.2026.8.26.0452</t>
+          <t>CONS-2026-01</t>
         </is>
       </c>
       <c r="B5" s="30" t="inlineStr">
@@ -2711,7 +2730,7 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr">
@@ -2721,33 +2740,29 @@
       </c>
       <c r="F5" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: cumprimento de sentença</t>
+          <t>Reunião com o cliente</t>
         </is>
       </c>
       <c r="G5" s="33">
-        <f>TODAY()+60</f>
-        <v/>
+        <f>TODAY()+9</f>
+        <v>46288.0</v>
       </c>
       <c r="H5" s="33">
-        <f>TODAY()-48</f>
-        <v/>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>Sem movimentação; verificar andamento</t>
-        </is>
-      </c>
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
+      </c>
+      <c r="I5" s="30" t="n"/>
       <c r="J5" s="28">
         <f>IF(OR(K5="",K5="Encerrado",K5="Sem próxima ação"),"",G5-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="25">
+        <v>9</v>
+      </c>
+      <c r="K5" s="25" t="str">
         <f>IF(A5="","",IF(D5="Encerrado","Encerrado",IF(G5="","Sem próxima ação",IF(G5&lt;Config!$B$5,"Atrasado",IF(G5=Config!$B$5,"Hoje",IF(G5-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L5" s="28">
         <f>IF(OR(A5="",D5="Encerrado",H5=""),"",Config!$B$5-H5)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M5" s="25">
         <f>IF(L5="","",IF(L5&gt;Config!$B$6,"Sim",""))</f>
@@ -2755,13 +2770,13 @@
       </c>
       <c r="N5" s="34">
         <f>IF(M5="Sim",L5-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
         <is>
-          <t>9225646-96.2026.8.26.0322</t>
+          <t>2998500-50.2026.8.26.0515</t>
         </is>
       </c>
       <c r="B6" s="30" t="inlineStr">
@@ -2776,7 +2791,7 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
@@ -2786,29 +2801,29 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: contrarrazões</t>
+          <t>Audiência de conciliação (confirmar presença do cliente)</t>
         </is>
       </c>
       <c r="G6" s="33">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+2</f>
+        <v>46281.0</v>
       </c>
       <c r="H6" s="33">
-        <f>TODAY()-5</f>
-        <v/>
+        <f>TODAY()-4</f>
+        <v>46275.0</v>
       </c>
       <c r="I6" s="30" t="n"/>
       <c r="J6" s="28">
         <f>IF(OR(K6="",K6="Encerrado",K6="Sem próxima ação"),"",G6-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K6" s="25">
+        <v>2</v>
+      </c>
+      <c r="K6" s="25" t="str">
         <f>IF(A6="","",IF(D6="Encerrado","Encerrado",IF(G6="","Sem próxima ação",IF(G6&lt;Config!$B$5,"Atrasado",IF(G6=Config!$B$5,"Hoje",IF(G6-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L6" s="28">
         <f>IF(OR(A6="",D6="Encerrado",H6=""),"",Config!$B$5-H6)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M6" s="25">
         <f>IF(L6="","",IF(L6&gt;Config!$B$6,"Sim",""))</f>
@@ -2816,13 +2831,13 @@
       </c>
       <c r="N6" s="34">
         <f>IF(M6="Sim",L6-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>6710873-21.2025.8.26.0571</t>
+          <t>9586960-92.2026.8.26.0106</t>
         </is>
       </c>
       <c r="B7" s="30" t="inlineStr">
@@ -2837,7 +2852,7 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr">
@@ -2847,29 +2862,29 @@
       </c>
       <c r="F7" s="30" t="inlineStr">
         <is>
-          <t>Reunião com o cliente</t>
+          <t>Protocolar: réplica</t>
         </is>
       </c>
       <c r="G7" s="33">
-        <f>TODAY()</f>
-        <v/>
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
       </c>
       <c r="H7" s="33">
-        <f>TODAY()-13</f>
-        <v/>
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
       </c>
       <c r="I7" s="30" t="n"/>
       <c r="J7" s="28">
         <f>IF(OR(K7="",K7="Encerrado",K7="Sem próxima ação"),"",G7-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K7" s="25">
+        <v>-3</v>
+      </c>
+      <c r="K7" s="25" t="str">
         <f>IF(A7="","",IF(D7="Encerrado","Encerrado",IF(G7="","Sem próxima ação",IF(G7&lt;Config!$B$5,"Atrasado",IF(G7=Config!$B$5,"Hoje",IF(G7-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L7" s="28">
         <f>IF(OR(A7="",D7="Encerrado",H7=""),"",Config!$B$5-H7)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M7" s="25">
         <f>IF(L7="","",IF(L7&gt;Config!$B$6,"Sim",""))</f>
@@ -2877,13 +2892,13 @@
       </c>
       <c r="N7" s="34">
         <f>IF(M7="Sim",L7-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>8735513-64.2025.8.26.0093</t>
+          <t>4746093-86.2026.8.26.0637</t>
         </is>
       </c>
       <c r="B8" s="30" t="inlineStr">
@@ -2898,7 +2913,7 @@
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
@@ -2908,29 +2923,29 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: alegações finais</t>
+          <t>Juntar documentos enviados pelo cliente</t>
         </is>
       </c>
       <c r="G8" s="33">
-        <f>TODAY()+15</f>
-        <v/>
+        <f>TODAY()+6</f>
+        <v>46285.0</v>
       </c>
       <c r="H8" s="33">
-        <f>TODAY()-21</f>
-        <v/>
+        <f>TODAY()-5</f>
+        <v>46274.0</v>
       </c>
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="28">
         <f>IF(OR(K8="",K8="Encerrado",K8="Sem próxima ação"),"",G8-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K8" s="25">
+        <v>6</v>
+      </c>
+      <c r="K8" s="25" t="str">
         <f>IF(A8="","",IF(D8="Encerrado","Encerrado",IF(G8="","Sem próxima ação",IF(G8&lt;Config!$B$5,"Atrasado",IF(G8=Config!$B$5,"Hoje",IF(G8-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L8" s="28">
         <f>IF(OR(A8="",D8="Encerrado",H8=""),"",Config!$B$5-H8)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M8" s="25">
         <f>IF(L8="","",IF(L8&gt;Config!$B$6,"Sim",""))</f>
@@ -2938,13 +2953,13 @@
       </c>
       <c r="N8" s="34">
         <f>IF(M8="Sim",L8-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>9802211-43.2025.8.26.0431</t>
+          <t>CONS-2026-02</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -2959,7 +2974,7 @@
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -2969,33 +2984,29 @@
       </c>
       <c r="F9" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: cumprimento de sentença</t>
+          <t>Entregar o parecer ao cliente</t>
         </is>
       </c>
       <c r="G9" s="33">
-        <f>TODAY()+35</f>
-        <v/>
+        <f>TODAY()+4</f>
+        <v>46283.0</v>
       </c>
       <c r="H9" s="33">
-        <f>TODAY()-41</f>
-        <v/>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t>Sem movimentação; verificar andamento</t>
-        </is>
-      </c>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
+      </c>
+      <c r="I9" s="30" t="n"/>
       <c r="J9" s="28">
         <f>IF(OR(K9="",K9="Encerrado",K9="Sem próxima ação"),"",G9-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K9" s="25">
+        <v>4</v>
+      </c>
+      <c r="K9" s="25" t="str">
         <f>IF(A9="","",IF(D9="Encerrado","Encerrado",IF(G9="","Sem próxima ação",IF(G9&lt;Config!$B$5,"Atrasado",IF(G9=Config!$B$5,"Hoje",IF(G9-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L9" s="28">
         <f>IF(OR(A9="",D9="Encerrado",H9=""),"",Config!$B$5-H9)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M9" s="25">
         <f>IF(L9="","",IF(L9&gt;Config!$B$6,"Sim",""))</f>
@@ -3003,56 +3014,60 @@
       </c>
       <c r="N9" s="34">
         <f>IF(M9="Sim",L9-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>9778116-95.2026.8.26.0106</t>
+          <t>CONS-2026-03</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
-        </is>
-      </c>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="n">
-        <v>46205</v>
-      </c>
-      <c r="I10" s="30" t="inlineStr">
-        <is>
-          <t>Encerrado; conferir checklist de encerramento</t>
-        </is>
-      </c>
+          <t>Rafael Lima</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Entregar o parecer ao cliente</t>
+        </is>
+      </c>
+      <c r="G10" s="33">
+        <f>TODAY()</f>
+        <v>46279.0</v>
+      </c>
+      <c r="H10" s="33">
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
+      </c>
+      <c r="I10" s="30" t="n"/>
       <c r="J10" s="28">
         <f>IF(OR(K10="",K10="Encerrado",K10="Sem próxima ação"),"",G10-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K10" s="25">
+        <v>0</v>
+      </c>
+      <c r="K10" s="25" t="str">
         <f>IF(A10="","",IF(D10="Encerrado","Encerrado",IF(G10="","Sem próxima ação",IF(G10&lt;Config!$B$5,"Atrasado",IF(G10=Config!$B$5,"Hoje",IF(G10-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="L10" s="28">
         <f>IF(OR(A10="",D10="Encerrado",H10=""),"",Config!$B$5-H10)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M10" s="25">
         <f>IF(L10="","",IF(L10&gt;Config!$B$6,"Sim",""))</f>
@@ -3060,64 +3075,60 @@
       </c>
       <c r="N10" s="34">
         <f>IF(M10="Sim",L10-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>8875326-79.2026.8.26.0258</t>
+          <t>CONS-2026-04</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F11" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: contrarrazões</t>
+          <t>Reunião com o cliente</t>
         </is>
       </c>
       <c r="G11" s="33">
-        <f>TODAY()+27</f>
-        <v/>
+        <f>TODAY()+3</f>
+        <v>46282.0</v>
       </c>
       <c r="H11" s="33">
-        <f>TODAY()-36</f>
-        <v/>
-      </c>
-      <c r="I11" s="30" t="inlineStr">
-        <is>
-          <t>Sem movimentação; verificar andamento</t>
-        </is>
-      </c>
+        <f>TODAY()-9</f>
+        <v>46270.0</v>
+      </c>
+      <c r="I11" s="30" t="n"/>
       <c r="J11" s="28">
         <f>IF(OR(K11="",K11="Encerrado",K11="Sem próxima ação"),"",G11-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K11" s="25">
+        <v>3</v>
+      </c>
+      <c r="K11" s="25" t="str">
         <f>IF(A11="","",IF(D11="Encerrado","Encerrado",IF(G11="","Sem próxima ação",IF(G11&lt;Config!$B$5,"Atrasado",IF(G11=Config!$B$5,"Hoje",IF(G11-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L11" s="28">
         <f>IF(OR(A11="",D11="Encerrado",H11=""),"",Config!$B$5-H11)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M11" s="25">
         <f>IF(L11="","",IF(L11&gt;Config!$B$6,"Sim",""))</f>
@@ -3125,60 +3136,60 @@
       </c>
       <c r="N11" s="34">
         <f>IF(M11="Sim",L11-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>4397912-47.2025.8.26.0276</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: cumprimento de sentença</t>
+          <t>Audiência de instrução (avisar testemunhas)</t>
         </is>
       </c>
       <c r="G12" s="33">
-        <f>TODAY()+18</f>
-        <v/>
+        <f>TODAY()+9</f>
+        <v>46288.0</v>
       </c>
       <c r="H12" s="33">
-        <f>TODAY()-4</f>
-        <v/>
+        <f>TODAY()-12</f>
+        <v>46267.0</v>
       </c>
       <c r="I12" s="30" t="n"/>
       <c r="J12" s="28">
         <f>IF(OR(K12="",K12="Encerrado",K12="Sem próxima ação"),"",G12-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K12" s="25">
+        <v>9</v>
+      </c>
+      <c r="K12" s="25" t="str">
         <f>IF(A12="","",IF(D12="Encerrado","Encerrado",IF(G12="","Sem próxima ação",IF(G12&lt;Config!$B$5,"Atrasado",IF(G12=Config!$B$5,"Hoje",IF(G12-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L12" s="28">
         <f>IF(OR(A12="",D12="Encerrado",H12=""),"",Config!$B$5-H12)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="M12" s="25">
         <f>IF(L12="","",IF(L12&gt;Config!$B$6,"Sim",""))</f>
@@ -3186,117 +3197,125 @@
       </c>
       <c r="N12" s="34">
         <f>IF(M12="Sim",L12-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>4352718-43.2025.8.26.0498</t>
+          <t>9236009-85.2025.8.26.0452</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
         <is>
-          <t>Enviar proposta de honorários</t>
+          <t>Iniciar o cumprimento de sentença</t>
         </is>
       </c>
       <c r="G13" s="33">
-        <f>TODAY()+6</f>
-        <v/>
+        <f>TODAY()+15</f>
+        <v>46294.0</v>
       </c>
       <c r="H13" s="33">
-        <f>TODAY()-52</f>
-        <v/>
-      </c>
-      <c r="I13" s="30" t="n"/>
+        <f>TODAY()-41</f>
+        <v>46238.0</v>
+      </c>
+      <c r="I13" s="30" t="inlineStr">
+        <is>
+          <t>Aguardando andamento da execução (penhora)</t>
+        </is>
+      </c>
       <c r="J13" s="28">
         <f>IF(OR(K13="",K13="Encerrado",K13="Sem próxima ação"),"",G13-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K13" s="25">
+        <v>15</v>
+      </c>
+      <c r="K13" s="25" t="str">
         <f>IF(A13="","",IF(D13="Encerrado","Encerrado",IF(G13="","Sem próxima ação",IF(G13&lt;Config!$B$5,"Atrasado",IF(G13=Config!$B$5,"Hoje",IF(G13-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L13" s="28">
         <f>IF(OR(A13="",D13="Encerrado",H13=""),"",Config!$B$5-H13)</f>
-        <v/>
-      </c>
-      <c r="M13" s="25">
+        <v>41</v>
+      </c>
+      <c r="M13" s="25" t="str">
         <f>IF(L13="","",IF(L13&gt;Config!$B$6,"Sim",""))</f>
-        <v/>
+        <v>Sim</v>
       </c>
       <c r="N13" s="34">
         <f>IF(M13="Sim",L13-ROW()/100000,0)</f>
-        <v/>
+        <v>40.99987</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>2650441-66.2026.8.26.0528</t>
+          <t>5025425-10.2025.8.26.0629</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
-        </is>
-      </c>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="33" t="n"/>
-      <c r="H14" s="33" t="n">
-        <v>46274</v>
-      </c>
-      <c r="I14" s="30" t="inlineStr">
-        <is>
-          <t>Encerrado; conferir checklist de encerramento</t>
-        </is>
-      </c>
+          <t>Marina Ferraz</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>Protocolar: embargos de declaração</t>
+        </is>
+      </c>
+      <c r="G14" s="33">
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
+      </c>
+      <c r="H14" s="33">
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
+      </c>
+      <c r="I14" s="30" t="n"/>
       <c r="J14" s="28">
         <f>IF(OR(K14="",K14="Encerrado",K14="Sem próxima ação"),"",G14-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K14" s="25">
+        <v>-1</v>
+      </c>
+      <c r="K14" s="25" t="str">
         <f>IF(A14="","",IF(D14="Encerrado","Encerrado",IF(G14="","Sem próxima ação",IF(G14&lt;Config!$B$5,"Atrasado",IF(G14=Config!$B$5,"Hoje",IF(G14-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L14" s="28">
         <f>IF(OR(A14="",D14="Encerrado",H14=""),"",Config!$B$5-H14)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M14" s="25">
         <f>IF(L14="","",IF(L14&gt;Config!$B$6,"Sim",""))</f>
@@ -3304,23 +3323,23 @@
       </c>
       <c r="N14" s="34">
         <f>IF(M14="Sim",L14-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>5470559-73.2026.8.26.0380</t>
+          <t>2354318-24.2026.8.26.0295</t>
         </is>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
@@ -3330,7 +3349,7 @@
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F15" s="30" t="inlineStr">
@@ -3339,25 +3358,25 @@
         </is>
       </c>
       <c r="G15" s="33">
-        <f>TODAY()</f>
-        <v/>
+        <f>TODAY()+8</f>
+        <v>46287.0</v>
       </c>
       <c r="H15" s="33">
-        <f>TODAY()-17</f>
-        <v/>
+        <f>TODAY()-7</f>
+        <v>46272.0</v>
       </c>
       <c r="I15" s="30" t="n"/>
       <c r="J15" s="28">
         <f>IF(OR(K15="",K15="Encerrado",K15="Sem próxima ação"),"",G15-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K15" s="25">
+        <v>8</v>
+      </c>
+      <c r="K15" s="25" t="str">
         <f>IF(A15="","",IF(D15="Encerrado","Encerrado",IF(G15="","Sem próxima ação",IF(G15&lt;Config!$B$5,"Atrasado",IF(G15=Config!$B$5,"Hoje",IF(G15-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L15" s="28">
         <f>IF(OR(A15="",D15="Encerrado",H15=""),"",Config!$B$5-H15)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M15" s="25">
         <f>IF(L15="","",IF(L15&gt;Config!$B$6,"Sim",""))</f>
@@ -3365,28 +3384,28 @@
       </c>
       <c r="N15" s="34">
         <f>IF(M15="Sim",L15-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>8570388-84.2025.8.26.0560</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
@@ -3396,29 +3415,29 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: contestação</t>
+          <t>Reunião com o cliente</t>
         </is>
       </c>
       <c r="G16" s="33">
-        <f>TODAY()</f>
-        <v/>
+        <f>TODAY()+5</f>
+        <v>46284.0</v>
       </c>
       <c r="H16" s="33">
-        <f>TODAY()-7</f>
-        <v/>
+        <f>TODAY()-8</f>
+        <v>46271.0</v>
       </c>
       <c r="I16" s="30" t="n"/>
       <c r="J16" s="28">
         <f>IF(OR(K16="",K16="Encerrado",K16="Sem próxima ação"),"",G16-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K16" s="25">
+        <v>5</v>
+      </c>
+      <c r="K16" s="25" t="str">
         <f>IF(A16="","",IF(D16="Encerrado","Encerrado",IF(G16="","Sem próxima ação",IF(G16&lt;Config!$B$5,"Atrasado",IF(G16=Config!$B$5,"Hoje",IF(G16-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L16" s="28">
         <f>IF(OR(A16="",D16="Encerrado",H16=""),"",Config!$B$5-H16)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="M16" s="25">
         <f>IF(L16="","",IF(L16&gt;Config!$B$6,"Sim",""))</f>
@@ -3426,23 +3445,23 @@
       </c>
       <c r="N16" s="34">
         <f>IF(M16="Sim",L16-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>6258696-95.2026.8.26.0598</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -3461,25 +3480,25 @@
         </is>
       </c>
       <c r="G17" s="33">
-        <f>TODAY()+2</f>
-        <v/>
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="H17" s="33">
-        <f>TODAY()-2</f>
-        <v/>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="I17" s="30" t="n"/>
       <c r="J17" s="28">
         <f>IF(OR(K17="",K17="Encerrado",K17="Sem próxima ação"),"",G17-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K17" s="25">
+        <v>0</v>
+      </c>
+      <c r="K17" s="25" t="str">
         <f>IF(A17="","",IF(D17="Encerrado","Encerrado",IF(G17="","Sem próxima ação",IF(G17&lt;Config!$B$5,"Atrasado",IF(G17=Config!$B$5,"Hoje",IF(G17-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="L17" s="28">
         <f>IF(OR(A17="",D17="Encerrado",H17=""),"",Config!$B$5-H17)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M17" s="25">
         <f>IF(L17="","",IF(L17&gt;Config!$B$6,"Sim",""))</f>
@@ -3487,28 +3506,28 @@
       </c>
       <c r="N17" s="34">
         <f>IF(M17="Sim",L17-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>9467819-47.2025.8.26.0087</t>
+          <t>9225646-96.2025.8.26.0322</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D18" s="32" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="E18" s="32" t="inlineStr">
@@ -3516,27 +3535,31 @@
           <t>Rafael Lima</t>
         </is>
       </c>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="33" t="n"/>
-      <c r="H18" s="33" t="n">
-        <v>45857</v>
-      </c>
-      <c r="I18" s="30" t="inlineStr">
-        <is>
-          <t>Encerrado; conferir checklist de encerramento</t>
-        </is>
-      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>Protocolar: manifestação sobre laudo</t>
+        </is>
+      </c>
+      <c r="G18" s="33">
+        <f>TODAY()+4</f>
+        <v>46283.0</v>
+      </c>
+      <c r="H18" s="33">
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
+      </c>
+      <c r="I18" s="30" t="n"/>
       <c r="J18" s="28">
         <f>IF(OR(K18="",K18="Encerrado",K18="Sem próxima ação"),"",G18-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K18" s="25">
+        <v>4</v>
+      </c>
+      <c r="K18" s="25" t="str">
         <f>IF(A18="","",IF(D18="Encerrado","Encerrado",IF(G18="","Sem próxima ação",IF(G18&lt;Config!$B$5,"Atrasado",IF(G18=Config!$B$5,"Hoje",IF(G18-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L18" s="28">
         <f>IF(OR(A18="",D18="Encerrado",H18=""),"",Config!$B$5-H18)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M18" s="25">
         <f>IF(L18="","",IF(L18&gt;Config!$B$6,"Sim",""))</f>
@@ -3544,18 +3567,18 @@
       </c>
       <c r="N18" s="34">
         <f>IF(M18="Sim",L18-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>4300029-58.2025.8.26.0015</t>
+          <t>4526984-60.2026.8.26.0258</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -3565,7 +3588,7 @@
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
@@ -3579,25 +3602,25 @@
         </is>
       </c>
       <c r="G19" s="33">
-        <f>TODAY()+2</f>
-        <v/>
+        <f>TODAY()+20</f>
+        <v>46299.0</v>
       </c>
       <c r="H19" s="33">
-        <f>TODAY()-14</f>
-        <v/>
+        <f>TODAY()-13</f>
+        <v>46266.0</v>
       </c>
       <c r="I19" s="30" t="n"/>
       <c r="J19" s="28">
         <f>IF(OR(K19="",K19="Encerrado",K19="Sem próxima ação"),"",G19-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K19" s="25">
+        <v>20</v>
+      </c>
+      <c r="K19" s="25" t="str">
         <f>IF(A19="","",IF(D19="Encerrado","Encerrado",IF(G19="","Sem próxima ação",IF(G19&lt;Config!$B$5,"Atrasado",IF(G19=Config!$B$5,"Hoje",IF(G19-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L19" s="28">
         <f>IF(OR(A19="",D19="Encerrado",H19=""),"",Config!$B$5-H19)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="M19" s="25">
         <f>IF(L19="","",IF(L19&gt;Config!$B$6,"Sim",""))</f>
@@ -3605,60 +3628,64 @@
       </c>
       <c r="N19" s="34">
         <f>IF(M19="Sim",L19-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>8986364-51.2026.8.26.0700</t>
+          <t>CONS-2026-06</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Audiência de conciliação (confirmar presença do cliente)</t>
+          <t>Reunião com o cliente</t>
         </is>
       </c>
       <c r="G20" s="33">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()-5</f>
+        <v>46274.0</v>
       </c>
       <c r="H20" s="33">
-        <f>TODAY()-14</f>
-        <v/>
-      </c>
-      <c r="I20" s="30" t="n"/>
+        <f>TODAY()-18</f>
+        <v>46261.0</v>
+      </c>
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>Cliente pediu para remarcar a reunião</t>
+        </is>
+      </c>
       <c r="J20" s="28">
         <f>IF(OR(K20="",K20="Encerrado",K20="Sem próxima ação"),"",G20-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K20" s="25">
+        <v>-5</v>
+      </c>
+      <c r="K20" s="25" t="str">
         <f>IF(A20="","",IF(D20="Encerrado","Encerrado",IF(G20="","Sem próxima ação",IF(G20&lt;Config!$B$5,"Atrasado",IF(G20=Config!$B$5,"Hoje",IF(G20-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L20" s="28">
         <f>IF(OR(A20="",D20="Encerrado",H20=""),"",Config!$B$5-H20)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="M20" s="25">
         <f>IF(L20="","",IF(L20&gt;Config!$B$6,"Sim",""))</f>
@@ -3666,28 +3693,28 @@
       </c>
       <c r="N20" s="34">
         <f>IF(M20="Sim",L20-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>9717671-36.2026.8.26.0445</t>
+          <t>6832730-55.2026.8.26.0386</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Acordo</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -3697,29 +3724,29 @@
       </c>
       <c r="F21" s="30" t="inlineStr">
         <is>
-          <t>Audiência de instrução (avisar testemunhas)</t>
+          <t>Enviar a minuta de acordo</t>
         </is>
       </c>
       <c r="G21" s="33">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="H21" s="33">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="I21" s="30" t="n"/>
       <c r="J21" s="28">
         <f>IF(OR(K21="",K21="Encerrado",K21="Sem próxima ação"),"",G21-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K21" s="25">
+        <v>0</v>
+      </c>
+      <c r="K21" s="25" t="str">
         <f>IF(A21="","",IF(D21="Encerrado","Encerrado",IF(G21="","Sem próxima ação",IF(G21&lt;Config!$B$5,"Atrasado",IF(G21=Config!$B$5,"Hoje",IF(G21-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="L21" s="28">
         <f>IF(OR(A21="",D21="Encerrado",H21=""),"",Config!$B$5-H21)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M21" s="25">
         <f>IF(L21="","",IF(L21&gt;Config!$B$6,"Sim",""))</f>
@@ -3727,23 +3754,23 @@
       </c>
       <c r="N21" s="34">
         <f>IF(M21="Sim",L21-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>1808451-67.2026.8.26.0657</t>
+          <t>9616569-91.2026.8.26.0079</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="D22" s="32" t="inlineStr">
@@ -3753,34 +3780,38 @@
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: contestação</t>
+          <t>Protocolar: impugnação</t>
         </is>
       </c>
       <c r="G22" s="33">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
       </c>
       <c r="H22" s="33">
-        <f>TODAY()-8</f>
-        <v/>
-      </c>
-      <c r="I22" s="30" t="n"/>
+        <f>TODAY()-4</f>
+        <v>46275.0</v>
+      </c>
+      <c r="I22" s="30" t="inlineStr">
+        <is>
+          <t>Aguardando documentos do cliente</t>
+        </is>
+      </c>
       <c r="J22" s="28">
         <f>IF(OR(K22="",K22="Encerrado",K22="Sem próxima ação"),"",G22-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K22" s="25">
+        <v>-2</v>
+      </c>
+      <c r="K22" s="25" t="str">
         <f>IF(A22="","",IF(D22="Encerrado","Encerrado",IF(G22="","Sem próxima ação",IF(G22&lt;Config!$B$5,"Atrasado",IF(G22=Config!$B$5,"Hoje",IF(G22-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L22" s="28">
         <f>IF(OR(A22="",D22="Encerrado",H22=""),"",Config!$B$5-H22)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M22" s="25">
         <f>IF(L22="","",IF(L22&gt;Config!$B$6,"Sim",""))</f>
@@ -3788,56 +3819,60 @@
       </c>
       <c r="N22" s="34">
         <f>IF(M22="Sim",L22-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>3310587-30.2026.8.26.0678</t>
+          <t>6710873-21.2025.8.26.0571</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
-        </is>
-      </c>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="33" t="n"/>
-      <c r="H23" s="33" t="n">
-        <v>46119</v>
-      </c>
-      <c r="I23" s="30" t="inlineStr">
-        <is>
-          <t>Encerrado; conferir checklist de encerramento</t>
-        </is>
-      </c>
+          <t>Marina Ferraz</t>
+        </is>
+      </c>
+      <c r="F23" s="30" t="inlineStr">
+        <is>
+          <t>Protocolar: recurso de apelação</t>
+        </is>
+      </c>
+      <c r="G23" s="33">
+        <f>TODAY()+2</f>
+        <v>46281.0</v>
+      </c>
+      <c r="H23" s="33">
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
+      </c>
+      <c r="I23" s="30" t="n"/>
       <c r="J23" s="28">
         <f>IF(OR(K23="",K23="Encerrado",K23="Sem próxima ação"),"",G23-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K23" s="25">
+        <v>2</v>
+      </c>
+      <c r="K23" s="25" t="str">
         <f>IF(A23="","",IF(D23="Encerrado","Encerrado",IF(G23="","Sem próxima ação",IF(G23&lt;Config!$B$5,"Atrasado",IF(G23=Config!$B$5,"Hoje",IF(G23-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L23" s="28">
         <f>IF(OR(A23="",D23="Encerrado",H23=""),"",Config!$B$5-H23)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M23" s="25">
         <f>IF(L23="","",IF(L23&gt;Config!$B$6,"Sim",""))</f>
@@ -3845,28 +3880,28 @@
       </c>
       <c r="N23" s="34">
         <f>IF(M23="Sim",L23-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>3930894-43.2025.8.26.0476</t>
+          <t>5900991-46.2026.8.26.0469</t>
         </is>
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Ana Beatriz Moreira</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="E24" s="32" t="inlineStr">
@@ -3876,29 +3911,29 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: alegações finais</t>
+          <t>Protocolar: manifestação sobre laudo</t>
         </is>
       </c>
       <c r="G24" s="33">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()-4</f>
+        <v>46275.0</v>
       </c>
       <c r="H24" s="33">
-        <f>TODAY()-18</f>
-        <v/>
+        <f>TODAY()-5</f>
+        <v>46274.0</v>
       </c>
       <c r="I24" s="30" t="n"/>
       <c r="J24" s="28">
         <f>IF(OR(K24="",K24="Encerrado",K24="Sem próxima ação"),"",G24-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K24" s="25">
+        <v>-4</v>
+      </c>
+      <c r="K24" s="25" t="str">
         <f>IF(A24="","",IF(D24="Encerrado","Encerrado",IF(G24="","Sem próxima ação",IF(G24&lt;Config!$B$5,"Atrasado",IF(G24=Config!$B$5,"Hoje",IF(G24-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L24" s="28">
         <f>IF(OR(A24="",D24="Encerrado",H24=""),"",Config!$B$5-H24)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M24" s="25">
         <f>IF(L24="","",IF(L24&gt;Config!$B$6,"Sim",""))</f>
@@ -3906,60 +3941,60 @@
       </c>
       <c r="N24" s="34">
         <f>IF(M24="Sim",L24-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>9802987-45.2025.8.26.0097</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D25" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F25" s="30" t="inlineStr">
         <is>
-          <t>Audiência de conciliação (confirmar presença do cliente)</t>
+          <t>Protocolar: alegações finais</t>
         </is>
       </c>
       <c r="G25" s="33">
-        <f>TODAY()+1</f>
-        <v/>
+        <f>TODAY()+10</f>
+        <v>46289.0</v>
       </c>
       <c r="H25" s="33">
-        <f>TODAY()-14</f>
-        <v/>
+        <f>TODAY()-9</f>
+        <v>46270.0</v>
       </c>
       <c r="I25" s="30" t="n"/>
       <c r="J25" s="28">
         <f>IF(OR(K25="",K25="Encerrado",K25="Sem próxima ação"),"",G25-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K25" s="25">
+        <v>10</v>
+      </c>
+      <c r="K25" s="25" t="str">
         <f>IF(A25="","",IF(D25="Encerrado","Encerrado",IF(G25="","Sem próxima ação",IF(G25&lt;Config!$B$5,"Atrasado",IF(G25=Config!$B$5,"Hoje",IF(G25-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L25" s="28">
         <f>IF(OR(A25="",D25="Encerrado",H25=""),"",Config!$B$5-H25)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="M25" s="25">
         <f>IF(L25="","",IF(L25&gt;Config!$B$6,"Sim",""))</f>
@@ -3967,18 +4002,18 @@
       </c>
       <c r="N25" s="34">
         <f>IF(M25="Sim",L25-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>6904743-30.2025.8.26.0361</t>
+          <t>6184138-13.2026.8.26.0378</t>
         </is>
       </c>
       <c r="B26" s="30" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -3988,7 +4023,7 @@
       </c>
       <c r="D26" s="32" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E26" s="32" t="inlineStr">
@@ -3998,58 +4033,62 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: contestação</t>
+          <t>Audiência de conciliação (confirmar presença do cliente)</t>
         </is>
       </c>
       <c r="G26" s="33">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="H26" s="33">
-        <f>TODAY()-2</f>
-        <v/>
-      </c>
-      <c r="I26" s="30" t="n"/>
+        <f>TODAY()-36</f>
+        <v>46243.0</v>
+      </c>
+      <c r="I26" s="30" t="inlineStr">
+        <is>
+          <t>Aguardando designação da audiência</t>
+        </is>
+      </c>
       <c r="J26" s="28">
         <f>IF(OR(K26="",K26="Encerrado",K26="Sem próxima ação"),"",G26-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K26" s="25">
+        <v>12</v>
+      </c>
+      <c r="K26" s="25" t="str">
         <f>IF(A26="","",IF(D26="Encerrado","Encerrado",IF(G26="","Sem próxima ação",IF(G26&lt;Config!$B$5,"Atrasado",IF(G26=Config!$B$5,"Hoje",IF(G26-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L26" s="28">
         <f>IF(OR(A26="",D26="Encerrado",H26=""),"",Config!$B$5-H26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="25">
+        <v>36</v>
+      </c>
+      <c r="M26" s="25" t="str">
         <f>IF(L26="","",IF(L26&gt;Config!$B$6,"Sim",""))</f>
-        <v/>
+        <v>Sim</v>
       </c>
       <c r="N26" s="34">
         <f>IF(M26="Sim",L26-ROW()/100000,0)</f>
-        <v/>
+        <v>35.99974</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>5497983-95.2025.8.26.0570</t>
+          <t>7099226-69.2026.8.26.0433</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
@@ -4059,29 +4098,29 @@
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: embargos</t>
+          <t>Juntar documentos enviados pelo cliente</t>
         </is>
       </c>
       <c r="G27" s="33">
-        <f>TODAY()+10</f>
-        <v/>
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
       </c>
       <c r="H27" s="33">
-        <f>TODAY()-19</f>
-        <v/>
+        <f>TODAY()-4</f>
+        <v>46275.0</v>
       </c>
       <c r="I27" s="30" t="n"/>
       <c r="J27" s="28">
         <f>IF(OR(K27="",K27="Encerrado",K27="Sem próxima ação"),"",G27-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K27" s="25">
+        <v>-6</v>
+      </c>
+      <c r="K27" s="25" t="str">
         <f>IF(A27="","",IF(D27="Encerrado","Encerrado",IF(G27="","Sem próxima ação",IF(G27&lt;Config!$B$5,"Atrasado",IF(G27=Config!$B$5,"Hoje",IF(G27-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L27" s="28">
         <f>IF(OR(A27="",D27="Encerrado",H27=""),"",Config!$B$5-H27)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="M27" s="25">
         <f>IF(L27="","",IF(L27&gt;Config!$B$6,"Sim",""))</f>
@@ -4089,93 +4128,93 @@
       </c>
       <c r="N27" s="34">
         <f>IF(M27="Sim",L27-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>4112092-92.2025.8.26.0646</t>
+          <t>2521428-61.2026.8.26.0600</t>
         </is>
       </c>
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Acordo</t>
         </is>
       </c>
       <c r="E28" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: alegações finais</t>
+          <t>Acompanhar a homologação do acordo</t>
         </is>
       </c>
       <c r="G28" s="33">
-        <f>TODAY()-1</f>
-        <v/>
+        <f>TODAY()+18</f>
+        <v>46297.0</v>
       </c>
       <c r="H28" s="33">
-        <f>TODAY()-4</f>
-        <v/>
+        <f>TODAY()-33</f>
+        <v>46246.0</v>
       </c>
       <c r="I28" s="30" t="inlineStr">
         <is>
-          <t>Aguardando documentos do cliente</t>
+          <t>Aguardando homologação do acordo pelo juízo</t>
         </is>
       </c>
       <c r="J28" s="28">
         <f>IF(OR(K28="",K28="Encerrado",K28="Sem próxima ação"),"",G28-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K28" s="25">
+        <v>18</v>
+      </c>
+      <c r="K28" s="25" t="str">
         <f>IF(A28="","",IF(D28="Encerrado","Encerrado",IF(G28="","Sem próxima ação",IF(G28&lt;Config!$B$5,"Atrasado",IF(G28=Config!$B$5,"Hoje",IF(G28-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L28" s="28">
         <f>IF(OR(A28="",D28="Encerrado",H28=""),"",Config!$B$5-H28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="25">
+        <v>33</v>
+      </c>
+      <c r="M28" s="25" t="str">
         <f>IF(L28="","",IF(L28&gt;Config!$B$6,"Sim",""))</f>
-        <v/>
+        <v>Sim</v>
       </c>
       <c r="N28" s="34">
         <f>IF(M28="Sim",L28-ROW()/100000,0)</f>
-        <v/>
+        <v>32.99972</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>5297049-18.2026.8.26.0015</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
         <is>
-          <t>Execução</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
@@ -4185,29 +4224,29 @@
       </c>
       <c r="F29" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: manifestação sobre laudo</t>
+          <t>Protocolar: contrarrazões</t>
         </is>
       </c>
       <c r="G29" s="33">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()+27</f>
+        <v>46306.0</v>
       </c>
       <c r="H29" s="33">
-        <f>TODAY()-8</f>
-        <v/>
+        <f>TODAY()-11</f>
+        <v>46268.0</v>
       </c>
       <c r="I29" s="30" t="n"/>
       <c r="J29" s="28">
         <f>IF(OR(K29="",K29="Encerrado",K29="Sem próxima ação"),"",G29-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K29" s="25">
+        <v>27</v>
+      </c>
+      <c r="K29" s="25" t="str">
         <f>IF(A29="","",IF(D29="Encerrado","Encerrado",IF(G29="","Sem próxima ação",IF(G29&lt;Config!$B$5,"Atrasado",IF(G29=Config!$B$5,"Hoje",IF(G29-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L29" s="28">
         <f>IF(OR(A29="",D29="Encerrado",H29=""),"",Config!$B$5-H29)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="M29" s="25">
         <f>IF(L29="","",IF(L29&gt;Config!$B$6,"Sim",""))</f>
@@ -4215,18 +4254,18 @@
       </c>
       <c r="N29" s="34">
         <f>IF(M29="Sim",L29-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>6877173-50.2026.8.26.0467</t>
+          <t>CONS-2026-07</t>
         </is>
       </c>
       <c r="B30" s="30" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -4236,7 +4275,7 @@
       </c>
       <c r="D30" s="32" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="E30" s="32" t="inlineStr">
@@ -4246,29 +4285,29 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: réplica</t>
+          <t>Entregar o parecer ao cliente</t>
         </is>
       </c>
       <c r="G30" s="33">
-        <f>TODAY()+1</f>
-        <v/>
+        <f>TODAY()+16</f>
+        <v>46295.0</v>
       </c>
       <c r="H30" s="33">
-        <f>TODAY()-21</f>
-        <v/>
+        <f>TODAY()-15</f>
+        <v>46264.0</v>
       </c>
       <c r="I30" s="30" t="n"/>
       <c r="J30" s="28">
         <f>IF(OR(K30="",K30="Encerrado",K30="Sem próxima ação"),"",G30-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K30" s="25">
+        <v>16</v>
+      </c>
+      <c r="K30" s="25" t="str">
         <f>IF(A30="","",IF(D30="Encerrado","Encerrado",IF(G30="","Sem próxima ação",IF(G30&lt;Config!$B$5,"Atrasado",IF(G30=Config!$B$5,"Hoje",IF(G30-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L30" s="28">
         <f>IF(OR(A30="",D30="Encerrado",H30=""),"",Config!$B$5-H30)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="M30" s="25">
         <f>IF(L30="","",IF(L30&gt;Config!$B$6,"Sim",""))</f>
@@ -4276,121 +4315,125 @@
       </c>
       <c r="N30" s="34">
         <f>IF(M30="Sim",L30-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>3003874-97.2026.8.26.0384</t>
+          <t>9495290-86.2025.8.26.0503</t>
         </is>
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D31" s="32" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>Reunião de alinhamento com o cliente</t>
+          <t>Iniciar o cumprimento de sentença</t>
         </is>
       </c>
       <c r="G31" s="33">
-        <f>TODAY()+14</f>
-        <v/>
+        <f>TODAY()+22</f>
+        <v>46301.0</v>
       </c>
       <c r="H31" s="33">
-        <f>TODAY()-21</f>
-        <v/>
-      </c>
-      <c r="I31" s="30" t="n"/>
+        <f>TODAY()-47</f>
+        <v>46232.0</v>
+      </c>
+      <c r="I31" s="30" t="inlineStr">
+        <is>
+          <t>Aguardando andamento da execução</t>
+        </is>
+      </c>
       <c r="J31" s="28">
         <f>IF(OR(K31="",K31="Encerrado",K31="Sem próxima ação"),"",G31-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K31" s="25">
+        <v>22</v>
+      </c>
+      <c r="K31" s="25" t="str">
         <f>IF(A31="","",IF(D31="Encerrado","Encerrado",IF(G31="","Sem próxima ação",IF(G31&lt;Config!$B$5,"Atrasado",IF(G31=Config!$B$5,"Hoje",IF(G31-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Em dia</v>
       </c>
       <c r="L31" s="28">
         <f>IF(OR(A31="",D31="Encerrado",H31=""),"",Config!$B$5-H31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="25">
+        <v>47</v>
+      </c>
+      <c r="M31" s="25" t="str">
         <f>IF(L31="","",IF(L31&gt;Config!$B$6,"Sim",""))</f>
-        <v/>
+        <v>Sim</v>
       </c>
       <c r="N31" s="34">
         <f>IF(M31="Sim",L31-ROW()/100000,0)</f>
-        <v/>
+        <v>46.99969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>6545676-47.2025.8.26.0126</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D32" s="32" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: manifestação sobre laudo</t>
+          <t>Protocolar: réplica</t>
         </is>
       </c>
       <c r="G32" s="33">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+1</f>
+        <v>46280.0</v>
       </c>
       <c r="H32" s="33">
-        <f>TODAY()-19</f>
-        <v/>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
       </c>
       <c r="I32" s="30" t="n"/>
       <c r="J32" s="28">
         <f>IF(OR(K32="",K32="Encerrado",K32="Sem próxima ação"),"",G32-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K32" s="25">
+        <v>1</v>
+      </c>
+      <c r="K32" s="25" t="str">
         <f>IF(A32="","",IF(D32="Encerrado","Encerrado",IF(G32="","Sem próxima ação",IF(G32&lt;Config!$B$5,"Atrasado",IF(G32=Config!$B$5,"Hoje",IF(G32-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L32" s="28">
         <f>IF(OR(A32="",D32="Encerrado",H32=""),"",Config!$B$5-H32)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M32" s="25">
         <f>IF(L32="","",IF(L32&gt;Config!$B$6,"Sim",""))</f>
@@ -4398,18 +4441,18 @@
       </c>
       <c r="N32" s="34">
         <f>IF(M32="Sim",L32-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>1941959-24.2026.8.26.0167</t>
+          <t>8045862-82.2026.8.26.0491</t>
         </is>
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Carlos Eduardo Nunes</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -4419,7 +4462,7 @@
       </c>
       <c r="D33" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
@@ -4429,29 +4472,29 @@
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>Audiência de conciliação (confirmar presença do cliente)</t>
+          <t>Protocolar: embargos de declaração</t>
         </is>
       </c>
       <c r="G33" s="33">
-        <f>TODAY()+4</f>
-        <v/>
+        <f>TODAY()+3</f>
+        <v>46282.0</v>
       </c>
       <c r="H33" s="33">
-        <f>TODAY()-2</f>
-        <v/>
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
       </c>
       <c r="I33" s="30" t="n"/>
       <c r="J33" s="28">
         <f>IF(OR(K33="",K33="Encerrado",K33="Sem próxima ação"),"",G33-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K33" s="25">
+        <v>3</v>
+      </c>
+      <c r="K33" s="25" t="str">
         <f>IF(A33="","",IF(D33="Encerrado","Encerrado",IF(G33="","Sem próxima ação",IF(G33&lt;Config!$B$5,"Atrasado",IF(G33=Config!$B$5,"Hoje",IF(G33-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="L33" s="28">
         <f>IF(OR(A33="",D33="Encerrado",H33=""),"",Config!$B$5-H33)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="M33" s="25">
         <f>IF(L33="","",IF(L33&gt;Config!$B$6,"Sim",""))</f>
@@ -4459,60 +4502,64 @@
       </c>
       <c r="N33" s="34">
         <f>IF(M33="Sim",L33-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>3118925-55.2025.8.26.0426</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D34" s="32" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="E34" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Protocolar: cumprimento de sentença</t>
+          <t>Protocolar: manifestação sobre o recurso</t>
         </is>
       </c>
       <c r="G34" s="33">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="H34" s="33">
-        <f>TODAY()-19</f>
-        <v/>
-      </c>
-      <c r="I34" s="30" t="n"/>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
+      </c>
+      <c r="I34" s="30" t="inlineStr">
+        <is>
+          <t>Aguardando documentos do cliente</t>
+        </is>
+      </c>
       <c r="J34" s="28">
         <f>IF(OR(K34="",K34="Encerrado",K34="Sem próxima ação"),"",G34-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="K34" s="25">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="25" t="str">
         <f>IF(A34="","",IF(D34="Encerrado","Encerrado",IF(G34="","Sem próxima ação",IF(G34&lt;Config!$B$5,"Atrasado",IF(G34=Config!$B$5,"Hoje",IF(G34-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="L34" s="28">
         <f>IF(OR(A34="",D34="Encerrado",H34=""),"",Config!$B$5-H34)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M34" s="25">
         <f>IF(L34="","",IF(L34&gt;Config!$B$6,"Sim",""))</f>
@@ -4520,18 +4567,18 @@
       </c>
       <c r="N34" s="34">
         <f>IF(M34="Sim",L34-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>7658179-42.2026.8.26.0152</t>
+          <t>4766902-26.2025.8.26.0051</t>
         </is>
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Padaria do Sol Ltda</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -4541,7 +4588,7 @@
       </c>
       <c r="D35" s="32" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
@@ -4549,27 +4596,23 @@
           <t>Marina Ferraz</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
-        <is>
-          <t>Protocolar: contrarrazões</t>
-        </is>
-      </c>
-      <c r="G35" s="33">
-        <f>TODAY()-3</f>
-        <v/>
-      </c>
-      <c r="H35" s="33">
-        <f>TODAY()-19</f>
-        <v/>
-      </c>
-      <c r="I35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="33" t="n"/>
+      <c r="H35" s="33" t="n">
+        <v>46106</v>
+      </c>
+      <c r="I35" s="30" t="inlineStr">
+        <is>
+          <t>Encerrado; conferir checklist de encerramento</t>
+        </is>
+      </c>
       <c r="J35" s="28">
         <f>IF(OR(K35="",K35="Encerrado",K35="Sem próxima ação"),"",G35-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="25" t="str">
         <f>IF(A35="","",IF(D35="Encerrado","Encerrado",IF(G35="","Sem próxima ação",IF(G35&lt;Config!$B$5,"Atrasado",IF(G35=Config!$B$5,"Hoje",IF(G35-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L35" s="28">
         <f>IF(OR(A35="",D35="Encerrado",H35=""),"",Config!$B$5-H35)</f>
@@ -4581,57 +4624,52 @@
       </c>
       <c r="N35" s="34">
         <f>IF(M35="Sim",L35-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
         <is>
-          <t>3326285-90.2025.8.26.0608</t>
+          <t>9778116-95.2025.8.26.0106</t>
         </is>
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
+          <t>Construtora Horizonte</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D36" s="32" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
-        </is>
-      </c>
-      <c r="F36" s="30" t="inlineStr">
-        <is>
-          <t>Aguardando retorno do cliente</t>
-        </is>
-      </c>
+          <t>Marina Ferraz</t>
+        </is>
+      </c>
+      <c r="F36" s="30" t="n"/>
       <c r="G36" s="33" t="n"/>
-      <c r="H36" s="33">
-        <f>TODAY()-13</f>
-        <v/>
+      <c r="H36" s="33" t="n">
+        <v>46142</v>
       </c>
       <c r="I36" s="30" t="inlineStr">
         <is>
-          <t>Cliente pediu tempo para decidir</t>
+          <t>Encerrado; conferir checklist de encerramento</t>
         </is>
       </c>
       <c r="J36" s="28">
         <f>IF(OR(K36="",K36="Encerrado",K36="Sem próxima ação"),"",G36-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="25" t="str">
         <f>IF(A36="","",IF(D36="Encerrado","Encerrado",IF(G36="","Sem próxima ação",IF(G36&lt;Config!$B$5,"Atrasado",IF(G36=Config!$B$5,"Hoje",IF(G36-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L36" s="28">
         <f>IF(OR(A36="",D36="Encerrado",H36=""),"",Config!$B$5-H36)</f>
@@ -4643,56 +4681,52 @@
       </c>
       <c r="N36" s="34">
         <f>IF(M36="Sim",L36-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="30" t="inlineStr">
         <is>
-          <t>1191416-90.2025.8.26.0249</t>
+          <t>8204296-70.2025.8.26.0146</t>
         </is>
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D37" s="32" t="inlineStr">
         <is>
-          <t>Instrução</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
-        </is>
-      </c>
-      <c r="F37" s="30" t="inlineStr">
-        <is>
-          <t>Protocolar: contrarrazões</t>
-        </is>
-      </c>
-      <c r="G37" s="33">
-        <f>TODAY()-1</f>
-        <v/>
-      </c>
-      <c r="H37" s="33">
-        <f>TODAY()-2</f>
-        <v/>
-      </c>
-      <c r="I37" s="30" t="n"/>
+          <t>Rafael Lima</t>
+        </is>
+      </c>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="33" t="n"/>
+      <c r="H37" s="33" t="n">
+        <v>46052</v>
+      </c>
+      <c r="I37" s="30" t="inlineStr">
+        <is>
+          <t>Encerrado; conferir checklist de encerramento</t>
+        </is>
+      </c>
       <c r="J37" s="28">
         <f>IF(OR(K37="",K37="Encerrado",K37="Sem próxima ação"),"",G37-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="25" t="str">
         <f>IF(A37="","",IF(D37="Encerrado","Encerrado",IF(G37="","Sem próxima ação",IF(G37&lt;Config!$B$5,"Atrasado",IF(G37=Config!$B$5,"Hoje",IF(G37-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L37" s="28">
         <f>IF(OR(A37="",D37="Encerrado",H37=""),"",Config!$B$5-H37)</f>
@@ -4704,18 +4738,18 @@
       </c>
       <c r="N37" s="34">
         <f>IF(M37="Sim",L37-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>5626517-53.2026.8.26.0206</t>
+          <t>9088515-39.2025.8.26.0125</t>
         </is>
       </c>
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Loja Verde Comércio</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -4725,7 +4759,7 @@
       </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
@@ -4733,27 +4767,23 @@
           <t>Marina Ferraz</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
-        <is>
-          <t>Enviar o resumo combinado ao cliente</t>
-        </is>
-      </c>
-      <c r="G38" s="33">
-        <f>TODAY()-2</f>
-        <v/>
-      </c>
-      <c r="H38" s="33">
-        <f>TODAY()-67</f>
-        <v/>
-      </c>
-      <c r="I38" s="30" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n">
+        <v>46185</v>
+      </c>
+      <c r="I38" s="30" t="inlineStr">
+        <is>
+          <t>Encerrado; conferir checklist de encerramento</t>
+        </is>
+      </c>
       <c r="J38" s="28">
         <f>IF(OR(K38="",K38="Encerrado",K38="Sem próxima ação"),"",G38-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="25" t="str">
         <f>IF(A38="","",IF(D38="Encerrado","Encerrado",IF(G38="","Sem próxima ação",IF(G38&lt;Config!$B$5,"Atrasado",IF(G38=Config!$B$5,"Hoje",IF(G38-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L38" s="28">
         <f>IF(OR(A38="",D38="Encerrado",H38=""),"",Config!$B$5-H38)</f>
@@ -4765,23 +4795,23 @@
       </c>
       <c r="N38" s="34">
         <f>IF(M38="Sim",L38-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="30" t="inlineStr">
         <is>
-          <t>6237740-34.2025.8.26.0163</t>
+          <t>8663770-96.2025.8.26.0481</t>
         </is>
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D39" s="32" t="inlineStr">
@@ -4797,7 +4827,7 @@
       <c r="F39" s="30" t="n"/>
       <c r="G39" s="33" t="n"/>
       <c r="H39" s="33" t="n">
-        <v>45862</v>
+        <v>46234</v>
       </c>
       <c r="I39" s="30" t="inlineStr">
         <is>
@@ -4808,9 +4838,9 @@
         <f>IF(OR(K39="",K39="Encerrado",K39="Sem próxima ação"),"",G39-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="25" t="str">
         <f>IF(A39="","",IF(D39="Encerrado","Encerrado",IF(G39="","Sem próxima ação",IF(G39&lt;Config!$B$5,"Atrasado",IF(G39=Config!$B$5,"Hoje",IF(G39-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L39" s="28">
         <f>IF(OR(A39="",D39="Encerrado",H39=""),"",Config!$B$5-H39)</f>
@@ -4822,23 +4852,23 @@
       </c>
       <c r="N39" s="34">
         <f>IF(M39="Sim",L39-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="30" t="inlineStr">
         <is>
-          <t>9778303-99.2026.8.26.0419</t>
+          <t>5211189-81.2025.8.26.0412</t>
         </is>
       </c>
       <c r="B40" s="30" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Fernanda Castro</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="D40" s="32" t="inlineStr">
@@ -4854,7 +4884,7 @@
       <c r="F40" s="30" t="n"/>
       <c r="G40" s="33" t="n"/>
       <c r="H40" s="33" t="n">
-        <v>46274</v>
+        <v>46248</v>
       </c>
       <c r="I40" s="30" t="inlineStr">
         <is>
@@ -4865,9 +4895,9 @@
         <f>IF(OR(K40="",K40="Encerrado",K40="Sem próxima ação"),"",G40-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="25" t="str">
         <f>IF(A40="","",IF(D40="Encerrado","Encerrado",IF(G40="","Sem próxima ação",IF(G40&lt;Config!$B$5,"Atrasado",IF(G40=Config!$B$5,"Hoje",IF(G40-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L40" s="28">
         <f>IF(OR(A40="",D40="Encerrado",H40=""),"",Config!$B$5-H40)</f>
@@ -4879,23 +4909,23 @@
       </c>
       <c r="N40" s="34">
         <f>IF(M40="Sim",L40-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
-          <t>3314594-22.2025.8.26.0019</t>
+          <t>6161129-80.2025.8.26.0663</t>
         </is>
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D41" s="32" t="inlineStr">
@@ -4905,13 +4935,13 @@
       </c>
       <c r="E41" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F41" s="30" t="n"/>
       <c r="G41" s="33" t="n"/>
       <c r="H41" s="33" t="n">
-        <v>46012</v>
+        <v>46199</v>
       </c>
       <c r="I41" s="30" t="inlineStr">
         <is>
@@ -4922,9 +4952,9 @@
         <f>IF(OR(K41="",K41="Encerrado",K41="Sem próxima ação"),"",G41-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K41" s="25">
+      <c r="K41" s="25" t="str">
         <f>IF(A41="","",IF(D41="Encerrado","Encerrado",IF(G41="","Sem próxima ação",IF(G41&lt;Config!$B$5,"Atrasado",IF(G41=Config!$B$5,"Hoje",IF(G41-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L41" s="28">
         <f>IF(OR(A41="",D41="Encerrado",H41=""),"",Config!$B$5-H41)</f>
@@ -4936,13 +4966,13 @@
       </c>
       <c r="N41" s="34">
         <f>IF(M41="Sim",L41-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t>7598076-58.2025.8.26.0552</t>
+          <t>9420478-99.2025.8.26.0491</t>
         </is>
       </c>
       <c r="B42" s="30" t="inlineStr">
@@ -4952,7 +4982,7 @@
       </c>
       <c r="C42" s="32" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D42" s="32" t="inlineStr">
@@ -4962,13 +4992,13 @@
       </c>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F42" s="30" t="n"/>
       <c r="G42" s="33" t="n"/>
       <c r="H42" s="33" t="n">
-        <v>46112</v>
+        <v>46094</v>
       </c>
       <c r="I42" s="30" t="inlineStr">
         <is>
@@ -4979,9 +5009,9 @@
         <f>IF(OR(K42="",K42="Encerrado",K42="Sem próxima ação"),"",G42-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="K42" s="25">
+      <c r="K42" s="25" t="str">
         <f>IF(A42="","",IF(D42="Encerrado","Encerrado",IF(G42="","Sem próxima ação",IF(G42&lt;Config!$B$5,"Atrasado",IF(G42=Config!$B$5,"Hoje",IF(G42-Config!$B$5&lt;=7,"Esta semana","Em dia"))))))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="L42" s="28">
         <f>IF(OR(A42="",D42="Encerrado",H42=""),"",Config!$B$5-H42)</f>
@@ -4993,7 +5023,7 @@
       </c>
       <c r="N42" s="34">
         <f>IF(M42="Sim",L42-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5024,7 +5054,7 @@
       </c>
       <c r="N43" s="34">
         <f>IF(M43="Sim",L43-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5055,7 +5085,7 @@
       </c>
       <c r="N44" s="34">
         <f>IF(M44="Sim",L44-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5086,7 +5116,7 @@
       </c>
       <c r="N45" s="34">
         <f>IF(M45="Sim",L45-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5117,7 +5147,7 @@
       </c>
       <c r="N46" s="34">
         <f>IF(M46="Sim",L46-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5148,7 +5178,7 @@
       </c>
       <c r="N47" s="34">
         <f>IF(M47="Sim",L47-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5179,7 +5209,7 @@
       </c>
       <c r="N48" s="34">
         <f>IF(M48="Sim",L48-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5210,7 +5240,7 @@
       </c>
       <c r="N49" s="34">
         <f>IF(M49="Sim",L49-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5241,7 +5271,7 @@
       </c>
       <c r="N50" s="34">
         <f>IF(M50="Sim",L50-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -5272,7 +5302,7 @@
       </c>
       <c r="N51" s="34">
         <f>IF(M51="Sim",L51-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -5303,7 +5333,7 @@
       </c>
       <c r="N52" s="34">
         <f>IF(M52="Sim",L52-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5334,7 +5364,7 @@
       </c>
       <c r="N53" s="34">
         <f>IF(M53="Sim",L53-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5365,7 +5395,7 @@
       </c>
       <c r="N54" s="34">
         <f>IF(M54="Sim",L54-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5396,7 +5426,7 @@
       </c>
       <c r="N55" s="34">
         <f>IF(M55="Sim",L55-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5427,7 +5457,7 @@
       </c>
       <c r="N56" s="34">
         <f>IF(M56="Sim",L56-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5458,7 +5488,7 @@
       </c>
       <c r="N57" s="34">
         <f>IF(M57="Sim",L57-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5489,7 +5519,7 @@
       </c>
       <c r="N58" s="34">
         <f>IF(M58="Sim",L58-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5520,7 +5550,7 @@
       </c>
       <c r="N59" s="34">
         <f>IF(M59="Sim",L59-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5551,7 +5581,7 @@
       </c>
       <c r="N60" s="34">
         <f>IF(M60="Sim",L60-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5582,7 +5612,7 @@
       </c>
       <c r="N61" s="34">
         <f>IF(M61="Sim",L61-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5613,7 +5643,7 @@
       </c>
       <c r="N62" s="34">
         <f>IF(M62="Sim",L62-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5644,7 +5674,7 @@
       </c>
       <c r="N63" s="34">
         <f>IF(M63="Sim",L63-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5675,7 +5705,7 @@
       </c>
       <c r="N64" s="34">
         <f>IF(M64="Sim",L64-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5706,7 +5736,7 @@
       </c>
       <c r="N65" s="34">
         <f>IF(M65="Sim",L65-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5737,7 +5767,7 @@
       </c>
       <c r="N66" s="34">
         <f>IF(M66="Sim",L66-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5768,7 +5798,7 @@
       </c>
       <c r="N67" s="34">
         <f>IF(M67="Sim",L67-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5799,7 +5829,7 @@
       </c>
       <c r="N68" s="34">
         <f>IF(M68="Sim",L68-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5830,7 +5860,7 @@
       </c>
       <c r="N69" s="34">
         <f>IF(M69="Sim",L69-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5861,7 +5891,7 @@
       </c>
       <c r="N70" s="34">
         <f>IF(M70="Sim",L70-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -5892,7 +5922,7 @@
       </c>
       <c r="N71" s="34">
         <f>IF(M71="Sim",L71-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5923,7 +5953,7 @@
       </c>
       <c r="N72" s="34">
         <f>IF(M72="Sim",L72-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5954,7 +5984,7 @@
       </c>
       <c r="N73" s="34">
         <f>IF(M73="Sim",L73-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -5985,7 +6015,7 @@
       </c>
       <c r="N74" s="34">
         <f>IF(M74="Sim",L74-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6016,7 +6046,7 @@
       </c>
       <c r="N75" s="34">
         <f>IF(M75="Sim",L75-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6047,7 +6077,7 @@
       </c>
       <c r="N76" s="34">
         <f>IF(M76="Sim",L76-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6078,7 +6108,7 @@
       </c>
       <c r="N77" s="34">
         <f>IF(M77="Sim",L77-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6109,7 +6139,7 @@
       </c>
       <c r="N78" s="34">
         <f>IF(M78="Sim",L78-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6140,7 +6170,7 @@
       </c>
       <c r="N79" s="34">
         <f>IF(M79="Sim",L79-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6171,7 +6201,7 @@
       </c>
       <c r="N80" s="34">
         <f>IF(M80="Sim",L80-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6202,7 +6232,7 @@
       </c>
       <c r="N81" s="34">
         <f>IF(M81="Sim",L81-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6233,7 +6263,7 @@
       </c>
       <c r="N82" s="34">
         <f>IF(M82="Sim",L82-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -6264,7 +6294,7 @@
       </c>
       <c r="N83" s="34">
         <f>IF(M83="Sim",L83-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6295,7 +6325,7 @@
       </c>
       <c r="N84" s="34">
         <f>IF(M84="Sim",L84-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -6326,7 +6356,7 @@
       </c>
       <c r="N85" s="34">
         <f>IF(M85="Sim",L85-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6357,7 +6387,7 @@
       </c>
       <c r="N86" s="34">
         <f>IF(M86="Sim",L86-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -6388,7 +6418,7 @@
       </c>
       <c r="N87" s="34">
         <f>IF(M87="Sim",L87-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -6419,7 +6449,7 @@
       </c>
       <c r="N88" s="34">
         <f>IF(M88="Sim",L88-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -6450,7 +6480,7 @@
       </c>
       <c r="N89" s="34">
         <f>IF(M89="Sim",L89-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -6481,7 +6511,7 @@
       </c>
       <c r="N90" s="34">
         <f>IF(M90="Sim",L90-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -6512,7 +6542,7 @@
       </c>
       <c r="N91" s="34">
         <f>IF(M91="Sim",L91-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -6543,7 +6573,7 @@
       </c>
       <c r="N92" s="34">
         <f>IF(M92="Sim",L92-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -6574,7 +6604,7 @@
       </c>
       <c r="N93" s="34">
         <f>IF(M93="Sim",L93-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -6605,7 +6635,7 @@
       </c>
       <c r="N94" s="34">
         <f>IF(M94="Sim",L94-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6636,7 +6666,7 @@
       </c>
       <c r="N95" s="34">
         <f>IF(M95="Sim",L95-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -6667,7 +6697,7 @@
       </c>
       <c r="N96" s="34">
         <f>IF(M96="Sim",L96-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -6698,7 +6728,7 @@
       </c>
       <c r="N97" s="34">
         <f>IF(M97="Sim",L97-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -6729,7 +6759,7 @@
       </c>
       <c r="N98" s="34">
         <f>IF(M98="Sim",L98-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6760,7 +6790,7 @@
       </c>
       <c r="N99" s="34">
         <f>IF(M99="Sim",L99-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -6791,7 +6821,7 @@
       </c>
       <c r="N100" s="34">
         <f>IF(M100="Sim",L100-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -6822,7 +6852,7 @@
       </c>
       <c r="N101" s="34">
         <f>IF(M101="Sim",L101-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -6853,7 +6883,7 @@
       </c>
       <c r="N102" s="34">
         <f>IF(M102="Sim",L102-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -6884,7 +6914,7 @@
       </c>
       <c r="N103" s="34">
         <f>IF(M103="Sim",L103-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6915,7 +6945,7 @@
       </c>
       <c r="N104" s="34">
         <f>IF(M104="Sim",L104-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -6946,7 +6976,7 @@
       </c>
       <c r="N105" s="34">
         <f>IF(M105="Sim",L105-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -6977,7 +7007,7 @@
       </c>
       <c r="N106" s="34">
         <f>IF(M106="Sim",L106-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -7008,7 +7038,7 @@
       </c>
       <c r="N107" s="34">
         <f>IF(M107="Sim",L107-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7069,7 @@
       </c>
       <c r="N108" s="34">
         <f>IF(M108="Sim",L108-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7070,7 +7100,7 @@
       </c>
       <c r="N109" s="34">
         <f>IF(M109="Sim",L109-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -7101,7 +7131,7 @@
       </c>
       <c r="N110" s="34">
         <f>IF(M110="Sim",L110-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7132,7 +7162,7 @@
       </c>
       <c r="N111" s="34">
         <f>IF(M111="Sim",L111-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -7163,7 +7193,7 @@
       </c>
       <c r="N112" s="34">
         <f>IF(M112="Sim",L112-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -7194,7 +7224,7 @@
       </c>
       <c r="N113" s="34">
         <f>IF(M113="Sim",L113-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -7225,7 +7255,7 @@
       </c>
       <c r="N114" s="34">
         <f>IF(M114="Sim",L114-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -7256,7 +7286,7 @@
       </c>
       <c r="N115" s="34">
         <f>IF(M115="Sim",L115-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7287,7 +7317,7 @@
       </c>
       <c r="N116" s="34">
         <f>IF(M116="Sim",L116-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7318,7 +7348,7 @@
       </c>
       <c r="N117" s="34">
         <f>IF(M117="Sim",L117-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -7349,7 +7379,7 @@
       </c>
       <c r="N118" s="34">
         <f>IF(M118="Sim",L118-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7380,7 +7410,7 @@
       </c>
       <c r="N119" s="34">
         <f>IF(M119="Sim",L119-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -7411,7 +7441,7 @@
       </c>
       <c r="N120" s="34">
         <f>IF(M120="Sim",L120-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -7442,7 +7472,7 @@
       </c>
       <c r="N121" s="34">
         <f>IF(M121="Sim",L121-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7473,7 +7503,7 @@
       </c>
       <c r="N122" s="34">
         <f>IF(M122="Sim",L122-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7504,7 +7534,7 @@
       </c>
       <c r="N123" s="34">
         <f>IF(M123="Sim",L123-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7535,7 +7565,7 @@
       </c>
       <c r="N124" s="34">
         <f>IF(M124="Sim",L124-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -7566,7 +7596,7 @@
       </c>
       <c r="N125" s="34">
         <f>IF(M125="Sim",L125-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7597,7 +7627,7 @@
       </c>
       <c r="N126" s="34">
         <f>IF(M126="Sim",L126-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7628,7 +7658,7 @@
       </c>
       <c r="N127" s="34">
         <f>IF(M127="Sim",L127-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7659,7 +7689,7 @@
       </c>
       <c r="N128" s="34">
         <f>IF(M128="Sim",L128-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7690,7 +7720,7 @@
       </c>
       <c r="N129" s="34">
         <f>IF(M129="Sim",L129-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -7721,7 +7751,7 @@
       </c>
       <c r="N130" s="34">
         <f>IF(M130="Sim",L130-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -7752,7 +7782,7 @@
       </c>
       <c r="N131" s="34">
         <f>IF(M131="Sim",L131-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7783,7 +7813,7 @@
       </c>
       <c r="N132" s="34">
         <f>IF(M132="Sim",L132-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -7814,7 +7844,7 @@
       </c>
       <c r="N133" s="34">
         <f>IF(M133="Sim",L133-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -7845,7 +7875,7 @@
       </c>
       <c r="N134" s="34">
         <f>IF(M134="Sim",L134-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7876,7 +7906,7 @@
       </c>
       <c r="N135" s="34">
         <f>IF(M135="Sim",L135-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -7907,7 +7937,7 @@
       </c>
       <c r="N136" s="34">
         <f>IF(M136="Sim",L136-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -7938,7 +7968,7 @@
       </c>
       <c r="N137" s="34">
         <f>IF(M137="Sim",L137-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -7969,7 +7999,7 @@
       </c>
       <c r="N138" s="34">
         <f>IF(M138="Sim",L138-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8000,7 +8030,7 @@
       </c>
       <c r="N139" s="34">
         <f>IF(M139="Sim",L139-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8031,7 +8061,7 @@
       </c>
       <c r="N140" s="34">
         <f>IF(M140="Sim",L140-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -8062,7 +8092,7 @@
       </c>
       <c r="N141" s="34">
         <f>IF(M141="Sim",L141-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -8093,7 +8123,7 @@
       </c>
       <c r="N142" s="34">
         <f>IF(M142="Sim",L142-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8124,7 +8154,7 @@
       </c>
       <c r="N143" s="34">
         <f>IF(M143="Sim",L143-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8155,7 +8185,7 @@
       </c>
       <c r="N144" s="34">
         <f>IF(M144="Sim",L144-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -8186,7 +8216,7 @@
       </c>
       <c r="N145" s="34">
         <f>IF(M145="Sim",L145-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8217,7 +8247,7 @@
       </c>
       <c r="N146" s="34">
         <f>IF(M146="Sim",L146-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8248,7 +8278,7 @@
       </c>
       <c r="N147" s="34">
         <f>IF(M147="Sim",L147-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8279,7 +8309,7 @@
       </c>
       <c r="N148" s="34">
         <f>IF(M148="Sim",L148-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -8310,7 +8340,7 @@
       </c>
       <c r="N149" s="34">
         <f>IF(M149="Sim",L149-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -8341,7 +8371,7 @@
       </c>
       <c r="N150" s="34">
         <f>IF(M150="Sim",L150-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -8372,7 +8402,7 @@
       </c>
       <c r="N151" s="34">
         <f>IF(M151="Sim",L151-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -8403,7 +8433,7 @@
       </c>
       <c r="N152" s="34">
         <f>IF(M152="Sim",L152-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -8434,7 +8464,7 @@
       </c>
       <c r="N153" s="34">
         <f>IF(M153="Sim",L153-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -8465,7 +8495,7 @@
       </c>
       <c r="N154" s="34">
         <f>IF(M154="Sim",L154-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -8496,7 +8526,7 @@
       </c>
       <c r="N155" s="34">
         <f>IF(M155="Sim",L155-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -8527,7 +8557,7 @@
       </c>
       <c r="N156" s="34">
         <f>IF(M156="Sim",L156-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -8558,7 +8588,7 @@
       </c>
       <c r="N157" s="34">
         <f>IF(M157="Sim",L157-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -8589,7 +8619,7 @@
       </c>
       <c r="N158" s="34">
         <f>IF(M158="Sim",L158-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -8620,7 +8650,7 @@
       </c>
       <c r="N159" s="34">
         <f>IF(M159="Sim",L159-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -8651,7 +8681,7 @@
       </c>
       <c r="N160" s="34">
         <f>IF(M160="Sim",L160-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -8682,7 +8712,7 @@
       </c>
       <c r="N161" s="34">
         <f>IF(M161="Sim",L161-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -8713,7 +8743,7 @@
       </c>
       <c r="N162" s="34">
         <f>IF(M162="Sim",L162-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -8744,7 +8774,7 @@
       </c>
       <c r="N163" s="34">
         <f>IF(M163="Sim",L163-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -8775,7 +8805,7 @@
       </c>
       <c r="N164" s="34">
         <f>IF(M164="Sim",L164-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -8806,7 +8836,7 @@
       </c>
       <c r="N165" s="34">
         <f>IF(M165="Sim",L165-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -8837,7 +8867,7 @@
       </c>
       <c r="N166" s="34">
         <f>IF(M166="Sim",L166-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -8868,7 +8898,7 @@
       </c>
       <c r="N167" s="34">
         <f>IF(M167="Sim",L167-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -8899,7 +8929,7 @@
       </c>
       <c r="N168" s="34">
         <f>IF(M168="Sim",L168-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -8930,7 +8960,7 @@
       </c>
       <c r="N169" s="34">
         <f>IF(M169="Sim",L169-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -8961,7 +8991,7 @@
       </c>
       <c r="N170" s="34">
         <f>IF(M170="Sim",L170-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -8992,7 +9022,7 @@
       </c>
       <c r="N171" s="34">
         <f>IF(M171="Sim",L171-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -9023,7 +9053,7 @@
       </c>
       <c r="N172" s="34">
         <f>IF(M172="Sim",L172-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -9054,7 +9084,7 @@
       </c>
       <c r="N173" s="34">
         <f>IF(M173="Sim",L173-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -9085,7 +9115,7 @@
       </c>
       <c r="N174" s="34">
         <f>IF(M174="Sim",L174-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -9116,7 +9146,7 @@
       </c>
       <c r="N175" s="34">
         <f>IF(M175="Sim",L175-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -9147,7 +9177,7 @@
       </c>
       <c r="N176" s="34">
         <f>IF(M176="Sim",L176-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -9178,7 +9208,7 @@
       </c>
       <c r="N177" s="34">
         <f>IF(M177="Sim",L177-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -9209,7 +9239,7 @@
       </c>
       <c r="N178" s="34">
         <f>IF(M178="Sim",L178-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -9240,7 +9270,7 @@
       </c>
       <c r="N179" s="34">
         <f>IF(M179="Sim",L179-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -9271,7 +9301,7 @@
       </c>
       <c r="N180" s="34">
         <f>IF(M180="Sim",L180-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -9302,7 +9332,7 @@
       </c>
       <c r="N181" s="34">
         <f>IF(M181="Sim",L181-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -9333,7 +9363,7 @@
       </c>
       <c r="N182" s="34">
         <f>IF(M182="Sim",L182-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -9364,7 +9394,7 @@
       </c>
       <c r="N183" s="34">
         <f>IF(M183="Sim",L183-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -9395,7 +9425,7 @@
       </c>
       <c r="N184" s="34">
         <f>IF(M184="Sim",L184-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -9426,7 +9456,7 @@
       </c>
       <c r="N185" s="34">
         <f>IF(M185="Sim",L185-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -9457,7 +9487,7 @@
       </c>
       <c r="N186" s="34">
         <f>IF(M186="Sim",L186-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -9488,7 +9518,7 @@
       </c>
       <c r="N187" s="34">
         <f>IF(M187="Sim",L187-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -9519,7 +9549,7 @@
       </c>
       <c r="N188" s="34">
         <f>IF(M188="Sim",L188-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -9550,7 +9580,7 @@
       </c>
       <c r="N189" s="34">
         <f>IF(M189="Sim",L189-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -9581,7 +9611,7 @@
       </c>
       <c r="N190" s="34">
         <f>IF(M190="Sim",L190-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -9612,7 +9642,7 @@
       </c>
       <c r="N191" s="34">
         <f>IF(M191="Sim",L191-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -9643,7 +9673,7 @@
       </c>
       <c r="N192" s="34">
         <f>IF(M192="Sim",L192-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -9674,7 +9704,7 @@
       </c>
       <c r="N193" s="34">
         <f>IF(M193="Sim",L193-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -9705,7 +9735,7 @@
       </c>
       <c r="N194" s="34">
         <f>IF(M194="Sim",L194-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -9736,7 +9766,7 @@
       </c>
       <c r="N195" s="34">
         <f>IF(M195="Sim",L195-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -9767,7 +9797,7 @@
       </c>
       <c r="N196" s="34">
         <f>IF(M196="Sim",L196-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -9798,7 +9828,7 @@
       </c>
       <c r="N197" s="34">
         <f>IF(M197="Sim",L197-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -9829,7 +9859,7 @@
       </c>
       <c r="N198" s="34">
         <f>IF(M198="Sim",L198-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -9860,7 +9890,7 @@
       </c>
       <c r="N199" s="34">
         <f>IF(M199="Sim",L199-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -9891,7 +9921,7 @@
       </c>
       <c r="N200" s="34">
         <f>IF(M200="Sim",L200-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -9922,7 +9952,7 @@
       </c>
       <c r="N201" s="34">
         <f>IF(M201="Sim",L201-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -9953,7 +9983,7 @@
       </c>
       <c r="N202" s="34">
         <f>IF(M202="Sim",L202-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -9984,7 +10014,7 @@
       </c>
       <c r="N203" s="34">
         <f>IF(M203="Sim",L203-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -10015,7 +10045,7 @@
       </c>
       <c r="N204" s="34">
         <f>IF(M204="Sim",L204-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -10046,7 +10076,7 @@
       </c>
       <c r="N205" s="34">
         <f>IF(M205="Sim",L205-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -10077,7 +10107,7 @@
       </c>
       <c r="N206" s="34">
         <f>IF(M206="Sim",L206-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -10108,7 +10138,7 @@
       </c>
       <c r="N207" s="34">
         <f>IF(M207="Sim",L207-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -10139,7 +10169,7 @@
       </c>
       <c r="N208" s="34">
         <f>IF(M208="Sim",L208-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -10170,7 +10200,7 @@
       </c>
       <c r="N209" s="34">
         <f>IF(M209="Sim",L209-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -10201,7 +10231,7 @@
       </c>
       <c r="N210" s="34">
         <f>IF(M210="Sim",L210-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -10232,7 +10262,7 @@
       </c>
       <c r="N211" s="34">
         <f>IF(M211="Sim",L211-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -10263,7 +10293,7 @@
       </c>
       <c r="N212" s="34">
         <f>IF(M212="Sim",L212-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -10294,7 +10324,7 @@
       </c>
       <c r="N213" s="34">
         <f>IF(M213="Sim",L213-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -10325,7 +10355,7 @@
       </c>
       <c r="N214" s="34">
         <f>IF(M214="Sim",L214-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -10356,7 +10386,7 @@
       </c>
       <c r="N215" s="34">
         <f>IF(M215="Sim",L215-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -10387,7 +10417,7 @@
       </c>
       <c r="N216" s="34">
         <f>IF(M216="Sim",L216-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -10418,7 +10448,7 @@
       </c>
       <c r="N217" s="34">
         <f>IF(M217="Sim",L217-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -10449,7 +10479,7 @@
       </c>
       <c r="N218" s="34">
         <f>IF(M218="Sim",L218-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -10480,7 +10510,7 @@
       </c>
       <c r="N219" s="34">
         <f>IF(M219="Sim",L219-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -10511,7 +10541,7 @@
       </c>
       <c r="N220" s="34">
         <f>IF(M220="Sim",L220-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -10542,7 +10572,7 @@
       </c>
       <c r="N221" s="34">
         <f>IF(M221="Sim",L221-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -10573,7 +10603,7 @@
       </c>
       <c r="N222" s="34">
         <f>IF(M222="Sim",L222-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -10604,7 +10634,7 @@
       </c>
       <c r="N223" s="34">
         <f>IF(M223="Sim",L223-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -10635,7 +10665,7 @@
       </c>
       <c r="N224" s="34">
         <f>IF(M224="Sim",L224-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -10666,7 +10696,7 @@
       </c>
       <c r="N225" s="34">
         <f>IF(M225="Sim",L225-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -10697,7 +10727,7 @@
       </c>
       <c r="N226" s="34">
         <f>IF(M226="Sim",L226-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -10728,7 +10758,7 @@
       </c>
       <c r="N227" s="34">
         <f>IF(M227="Sim",L227-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -10759,7 +10789,7 @@
       </c>
       <c r="N228" s="34">
         <f>IF(M228="Sim",L228-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -10790,7 +10820,7 @@
       </c>
       <c r="N229" s="34">
         <f>IF(M229="Sim",L229-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -10821,7 +10851,7 @@
       </c>
       <c r="N230" s="34">
         <f>IF(M230="Sim",L230-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -10852,7 +10882,7 @@
       </c>
       <c r="N231" s="34">
         <f>IF(M231="Sim",L231-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -10883,7 +10913,7 @@
       </c>
       <c r="N232" s="34">
         <f>IF(M232="Sim",L232-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -10914,7 +10944,7 @@
       </c>
       <c r="N233" s="34">
         <f>IF(M233="Sim",L233-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -10945,7 +10975,7 @@
       </c>
       <c r="N234" s="34">
         <f>IF(M234="Sim",L234-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -10976,7 +11006,7 @@
       </c>
       <c r="N235" s="34">
         <f>IF(M235="Sim",L235-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -11007,7 +11037,7 @@
       </c>
       <c r="N236" s="34">
         <f>IF(M236="Sim",L236-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -11038,7 +11068,7 @@
       </c>
       <c r="N237" s="34">
         <f>IF(M237="Sim",L237-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -11069,7 +11099,7 @@
       </c>
       <c r="N238" s="34">
         <f>IF(M238="Sim",L238-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -11100,7 +11130,7 @@
       </c>
       <c r="N239" s="34">
         <f>IF(M239="Sim",L239-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -11131,7 +11161,7 @@
       </c>
       <c r="N240" s="34">
         <f>IF(M240="Sim",L240-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -11162,7 +11192,7 @@
       </c>
       <c r="N241" s="34">
         <f>IF(M241="Sim",L241-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -11193,7 +11223,7 @@
       </c>
       <c r="N242" s="34">
         <f>IF(M242="Sim",L242-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -11224,7 +11254,7 @@
       </c>
       <c r="N243" s="34">
         <f>IF(M243="Sim",L243-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -11255,7 +11285,7 @@
       </c>
       <c r="N244" s="34">
         <f>IF(M244="Sim",L244-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -11286,7 +11316,7 @@
       </c>
       <c r="N245" s="34">
         <f>IF(M245="Sim",L245-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -11317,7 +11347,7 @@
       </c>
       <c r="N246" s="34">
         <f>IF(M246="Sim",L246-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -11348,7 +11378,7 @@
       </c>
       <c r="N247" s="34">
         <f>IF(M247="Sim",L247-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -11379,7 +11409,7 @@
       </c>
       <c r="N248" s="34">
         <f>IF(M248="Sim",L248-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -11410,7 +11440,7 @@
       </c>
       <c r="N249" s="34">
         <f>IF(M249="Sim",L249-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -11441,7 +11471,7 @@
       </c>
       <c r="N250" s="34">
         <f>IF(M250="Sim",L250-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -11472,7 +11502,7 @@
       </c>
       <c r="N251" s="34">
         <f>IF(M251="Sim",L251-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -11503,7 +11533,7 @@
       </c>
       <c r="N252" s="34">
         <f>IF(M252="Sim",L252-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -11534,7 +11564,7 @@
       </c>
       <c r="N253" s="34">
         <f>IF(M253="Sim",L253-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -11565,7 +11595,7 @@
       </c>
       <c r="N254" s="34">
         <f>IF(M254="Sim",L254-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -11596,7 +11626,7 @@
       </c>
       <c r="N255" s="34">
         <f>IF(M255="Sim",L255-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -11627,7 +11657,7 @@
       </c>
       <c r="N256" s="34">
         <f>IF(M256="Sim",L256-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -11658,7 +11688,7 @@
       </c>
       <c r="N257" s="34">
         <f>IF(M257="Sim",L257-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -11689,7 +11719,7 @@
       </c>
       <c r="N258" s="34">
         <f>IF(M258="Sim",L258-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -11720,7 +11750,7 @@
       </c>
       <c r="N259" s="34">
         <f>IF(M259="Sim",L259-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -11751,7 +11781,7 @@
       </c>
       <c r="N260" s="34">
         <f>IF(M260="Sim",L260-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -11782,7 +11812,7 @@
       </c>
       <c r="N261" s="34">
         <f>IF(M261="Sim",L261-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -11813,7 +11843,7 @@
       </c>
       <c r="N262" s="34">
         <f>IF(M262="Sim",L262-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -11844,7 +11874,7 @@
       </c>
       <c r="N263" s="34">
         <f>IF(M263="Sim",L263-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -11875,7 +11905,7 @@
       </c>
       <c r="N264" s="34">
         <f>IF(M264="Sim",L264-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -11906,7 +11936,7 @@
       </c>
       <c r="N265" s="34">
         <f>IF(M265="Sim",L265-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -11937,7 +11967,7 @@
       </c>
       <c r="N266" s="34">
         <f>IF(M266="Sim",L266-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -11968,7 +11998,7 @@
       </c>
       <c r="N267" s="34">
         <f>IF(M267="Sim",L267-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -11999,7 +12029,7 @@
       </c>
       <c r="N268" s="34">
         <f>IF(M268="Sim",L268-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -12030,7 +12060,7 @@
       </c>
       <c r="N269" s="34">
         <f>IF(M269="Sim",L269-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -12061,7 +12091,7 @@
       </c>
       <c r="N270" s="34">
         <f>IF(M270="Sim",L270-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -12092,7 +12122,7 @@
       </c>
       <c r="N271" s="34">
         <f>IF(M271="Sim",L271-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -12123,7 +12153,7 @@
       </c>
       <c r="N272" s="34">
         <f>IF(M272="Sim",L272-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -12154,7 +12184,7 @@
       </c>
       <c r="N273" s="34">
         <f>IF(M273="Sim",L273-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -12185,7 +12215,7 @@
       </c>
       <c r="N274" s="34">
         <f>IF(M274="Sim",L274-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -12216,7 +12246,7 @@
       </c>
       <c r="N275" s="34">
         <f>IF(M275="Sim",L275-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -12247,7 +12277,7 @@
       </c>
       <c r="N276" s="34">
         <f>IF(M276="Sim",L276-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -12278,7 +12308,7 @@
       </c>
       <c r="N277" s="34">
         <f>IF(M277="Sim",L277-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -12309,7 +12339,7 @@
       </c>
       <c r="N278" s="34">
         <f>IF(M278="Sim",L278-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -12340,7 +12370,7 @@
       </c>
       <c r="N279" s="34">
         <f>IF(M279="Sim",L279-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -12371,7 +12401,7 @@
       </c>
       <c r="N280" s="34">
         <f>IF(M280="Sim",L280-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -12402,7 +12432,7 @@
       </c>
       <c r="N281" s="34">
         <f>IF(M281="Sim",L281-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -12433,7 +12463,7 @@
       </c>
       <c r="N282" s="34">
         <f>IF(M282="Sim",L282-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -12464,7 +12494,7 @@
       </c>
       <c r="N283" s="34">
         <f>IF(M283="Sim",L283-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -12495,7 +12525,7 @@
       </c>
       <c r="N284" s="34">
         <f>IF(M284="Sim",L284-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -12526,7 +12556,7 @@
       </c>
       <c r="N285" s="34">
         <f>IF(M285="Sim",L285-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -12557,7 +12587,7 @@
       </c>
       <c r="N286" s="34">
         <f>IF(M286="Sim",L286-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -12588,7 +12618,7 @@
       </c>
       <c r="N287" s="34">
         <f>IF(M287="Sim",L287-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -12619,7 +12649,7 @@
       </c>
       <c r="N288" s="34">
         <f>IF(M288="Sim",L288-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -12650,7 +12680,7 @@
       </c>
       <c r="N289" s="34">
         <f>IF(M289="Sim",L289-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -12681,7 +12711,7 @@
       </c>
       <c r="N290" s="34">
         <f>IF(M290="Sim",L290-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -12712,7 +12742,7 @@
       </c>
       <c r="N291" s="34">
         <f>IF(M291="Sim",L291-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -12743,7 +12773,7 @@
       </c>
       <c r="N292" s="34">
         <f>IF(M292="Sim",L292-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -12774,7 +12804,7 @@
       </c>
       <c r="N293" s="34">
         <f>IF(M293="Sim",L293-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -12805,7 +12835,7 @@
       </c>
       <c r="N294" s="34">
         <f>IF(M294="Sim",L294-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -12836,7 +12866,7 @@
       </c>
       <c r="N295" s="34">
         <f>IF(M295="Sim",L295-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -12867,7 +12897,7 @@
       </c>
       <c r="N296" s="34">
         <f>IF(M296="Sim",L296-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -12898,7 +12928,7 @@
       </c>
       <c r="N297" s="34">
         <f>IF(M297="Sim",L297-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -12929,7 +12959,7 @@
       </c>
       <c r="N298" s="34">
         <f>IF(M298="Sim",L298-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -12960,7 +12990,7 @@
       </c>
       <c r="N299" s="34">
         <f>IF(M299="Sim",L299-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -12991,7 +13021,7 @@
       </c>
       <c r="N300" s="34">
         <f>IF(M300="Sim",L300-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -13022,7 +13052,7 @@
       </c>
       <c r="N301" s="34">
         <f>IF(M301="Sim",L301-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -13053,7 +13083,7 @@
       </c>
       <c r="N302" s="34">
         <f>IF(M302="Sim",L302-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -13084,7 +13114,7 @@
       </c>
       <c r="N303" s="34">
         <f>IF(M303="Sim",L303-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -13115,7 +13145,7 @@
       </c>
       <c r="N304" s="34">
         <f>IF(M304="Sim",L304-ROW()/100000,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -254,7 +255,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,14 +266,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -691,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -864,17 +865,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2421,9 +2434,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="31">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="31" t="n">
+        <v>46279</v>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
@@ -2743,13 +2755,11 @@
           <t>Reunião com o cliente</t>
         </is>
       </c>
-      <c r="G5" s="33">
-        <f>TODAY()+9</f>
-        <v>46288.0</v>
-      </c>
-      <c r="H5" s="33">
-        <f>TODAY()-6</f>
-        <v>46273.0</v>
+      <c r="G5" s="33" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H5" s="33" t="n">
+        <v>46273</v>
       </c>
       <c r="I5" s="30" t="n"/>
       <c r="J5" s="28">
@@ -2804,13 +2814,11 @@
           <t>Audiência de conciliação (confirmar presença do cliente)</t>
         </is>
       </c>
-      <c r="G6" s="33">
-        <f>TODAY()+2</f>
-        <v>46281.0</v>
-      </c>
-      <c r="H6" s="33">
-        <f>TODAY()-4</f>
-        <v>46275.0</v>
+      <c r="G6" s="33" t="n">
+        <v>46281</v>
+      </c>
+      <c r="H6" s="33" t="n">
+        <v>46275</v>
       </c>
       <c r="I6" s="30" t="n"/>
       <c r="J6" s="28">
@@ -2865,13 +2873,11 @@
           <t>Protocolar: réplica</t>
         </is>
       </c>
-      <c r="G7" s="33">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
-      </c>
-      <c r="H7" s="33">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
+      <c r="G7" s="33" t="n">
+        <v>46276</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>46276</v>
       </c>
       <c r="I7" s="30" t="n"/>
       <c r="J7" s="28">
@@ -2926,13 +2932,11 @@
           <t>Juntar documentos enviados pelo cliente</t>
         </is>
       </c>
-      <c r="G8" s="33">
-        <f>TODAY()+6</f>
-        <v>46285.0</v>
-      </c>
-      <c r="H8" s="33">
-        <f>TODAY()-5</f>
-        <v>46274.0</v>
+      <c r="G8" s="33" t="n">
+        <v>46285</v>
+      </c>
+      <c r="H8" s="33" t="n">
+        <v>46274</v>
       </c>
       <c r="I8" s="30" t="n"/>
       <c r="J8" s="28">
@@ -2987,13 +2991,11 @@
           <t>Entregar o parecer ao cliente</t>
         </is>
       </c>
-      <c r="G9" s="33">
-        <f>TODAY()+4</f>
-        <v>46283.0</v>
-      </c>
-      <c r="H9" s="33">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+      <c r="G9" s="33" t="n">
+        <v>46283</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>46277</v>
       </c>
       <c r="I9" s="30" t="n"/>
       <c r="J9" s="28">
@@ -3048,13 +3050,11 @@
           <t>Entregar o parecer ao cliente</t>
         </is>
       </c>
-      <c r="G10" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
-      </c>
-      <c r="H10" s="33">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+      <c r="G10" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>46278</v>
       </c>
       <c r="I10" s="30" t="n"/>
       <c r="J10" s="28">
@@ -3109,13 +3109,11 @@
           <t>Reunião com o cliente</t>
         </is>
       </c>
-      <c r="G11" s="33">
-        <f>TODAY()+3</f>
-        <v>46282.0</v>
-      </c>
-      <c r="H11" s="33">
-        <f>TODAY()-9</f>
-        <v>46270.0</v>
+      <c r="G11" s="33" t="n">
+        <v>46282</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>46270</v>
       </c>
       <c r="I11" s="30" t="n"/>
       <c r="J11" s="28">
@@ -3170,13 +3168,11 @@
           <t>Audiência de instrução (avisar testemunhas)</t>
         </is>
       </c>
-      <c r="G12" s="33">
-        <f>TODAY()+9</f>
-        <v>46288.0</v>
-      </c>
-      <c r="H12" s="33">
-        <f>TODAY()-12</f>
-        <v>46267.0</v>
+      <c r="G12" s="33" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>46267</v>
       </c>
       <c r="I12" s="30" t="n"/>
       <c r="J12" s="28">
@@ -3231,13 +3227,11 @@
           <t>Iniciar o cumprimento de sentença</t>
         </is>
       </c>
-      <c r="G13" s="33">
-        <f>TODAY()+15</f>
-        <v>46294.0</v>
-      </c>
-      <c r="H13" s="33">
-        <f>TODAY()-41</f>
-        <v>46238.0</v>
+      <c r="G13" s="33" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>46238</v>
       </c>
       <c r="I13" s="30" t="inlineStr">
         <is>
@@ -3296,13 +3290,11 @@
           <t>Protocolar: embargos de declaração</t>
         </is>
       </c>
-      <c r="G14" s="33">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
-      </c>
-      <c r="H14" s="33">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+      <c r="G14" s="33" t="n">
+        <v>46278</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <v>46277</v>
       </c>
       <c r="I14" s="30" t="n"/>
       <c r="J14" s="28">
@@ -3357,13 +3349,11 @@
           <t>Protocolar: contrarrazões</t>
         </is>
       </c>
-      <c r="G15" s="33">
-        <f>TODAY()+8</f>
-        <v>46287.0</v>
-      </c>
-      <c r="H15" s="33">
-        <f>TODAY()-7</f>
-        <v>46272.0</v>
+      <c r="G15" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>46272</v>
       </c>
       <c r="I15" s="30" t="n"/>
       <c r="J15" s="28">
@@ -3418,13 +3408,11 @@
           <t>Reunião com o cliente</t>
         </is>
       </c>
-      <c r="G16" s="33">
-        <f>TODAY()+5</f>
-        <v>46284.0</v>
-      </c>
-      <c r="H16" s="33">
-        <f>TODAY()-8</f>
-        <v>46271.0</v>
+      <c r="G16" s="33" t="n">
+        <v>46284</v>
+      </c>
+      <c r="H16" s="33" t="n">
+        <v>46271</v>
       </c>
       <c r="I16" s="30" t="n"/>
       <c r="J16" s="28">
@@ -3479,13 +3467,11 @@
           <t>Protocolar: contestação</t>
         </is>
       </c>
-      <c r="G17" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
-      </c>
-      <c r="H17" s="33">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+      <c r="G17" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H17" s="33" t="n">
+        <v>46278</v>
       </c>
       <c r="I17" s="30" t="n"/>
       <c r="J17" s="28">
@@ -3540,13 +3526,11 @@
           <t>Protocolar: manifestação sobre laudo</t>
         </is>
       </c>
-      <c r="G18" s="33">
-        <f>TODAY()+4</f>
-        <v>46283.0</v>
-      </c>
-      <c r="H18" s="33">
-        <f>TODAY()-6</f>
-        <v>46273.0</v>
+      <c r="G18" s="33" t="n">
+        <v>46283</v>
+      </c>
+      <c r="H18" s="33" t="n">
+        <v>46273</v>
       </c>
       <c r="I18" s="30" t="n"/>
       <c r="J18" s="28">
@@ -3601,13 +3585,11 @@
           <t>Audiência de conciliação (confirmar presença do cliente)</t>
         </is>
       </c>
-      <c r="G19" s="33">
-        <f>TODAY()+20</f>
-        <v>46299.0</v>
-      </c>
-      <c r="H19" s="33">
-        <f>TODAY()-13</f>
-        <v>46266.0</v>
+      <c r="G19" s="33" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H19" s="33" t="n">
+        <v>46266</v>
       </c>
       <c r="I19" s="30" t="n"/>
       <c r="J19" s="28">
@@ -3662,13 +3644,11 @@
           <t>Reunião com o cliente</t>
         </is>
       </c>
-      <c r="G20" s="33">
-        <f>TODAY()-5</f>
-        <v>46274.0</v>
-      </c>
-      <c r="H20" s="33">
-        <f>TODAY()-18</f>
-        <v>46261.0</v>
+      <c r="G20" s="33" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H20" s="33" t="n">
+        <v>46261</v>
       </c>
       <c r="I20" s="30" t="inlineStr">
         <is>
@@ -3727,13 +3707,11 @@
           <t>Enviar a minuta de acordo</t>
         </is>
       </c>
-      <c r="G21" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
-      </c>
-      <c r="H21" s="33">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+      <c r="G21" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H21" s="33" t="n">
+        <v>46278</v>
       </c>
       <c r="I21" s="30" t="n"/>
       <c r="J21" s="28">
@@ -3788,13 +3766,11 @@
           <t>Protocolar: impugnação</t>
         </is>
       </c>
-      <c r="G22" s="33">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
-      </c>
-      <c r="H22" s="33">
-        <f>TODAY()-4</f>
-        <v>46275.0</v>
+      <c r="G22" s="33" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H22" s="33" t="n">
+        <v>46275</v>
       </c>
       <c r="I22" s="30" t="inlineStr">
         <is>
@@ -3853,13 +3829,11 @@
           <t>Protocolar: recurso de apelação</t>
         </is>
       </c>
-      <c r="G23" s="33">
-        <f>TODAY()+2</f>
-        <v>46281.0</v>
-      </c>
-      <c r="H23" s="33">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
+      <c r="G23" s="33" t="n">
+        <v>46281</v>
+      </c>
+      <c r="H23" s="33" t="n">
+        <v>46276</v>
       </c>
       <c r="I23" s="30" t="n"/>
       <c r="J23" s="28">
@@ -3914,13 +3888,11 @@
           <t>Protocolar: manifestação sobre laudo</t>
         </is>
       </c>
-      <c r="G24" s="33">
-        <f>TODAY()-4</f>
-        <v>46275.0</v>
-      </c>
-      <c r="H24" s="33">
-        <f>TODAY()-5</f>
-        <v>46274.0</v>
+      <c r="G24" s="33" t="n">
+        <v>46275</v>
+      </c>
+      <c r="H24" s="33" t="n">
+        <v>46274</v>
       </c>
       <c r="I24" s="30" t="n"/>
       <c r="J24" s="28">
@@ -3975,13 +3947,11 @@
           <t>Protocolar: alegações finais</t>
         </is>
       </c>
-      <c r="G25" s="33">
-        <f>TODAY()+10</f>
-        <v>46289.0</v>
-      </c>
-      <c r="H25" s="33">
-        <f>TODAY()-9</f>
-        <v>46270.0</v>
+      <c r="G25" s="33" t="n">
+        <v>46289</v>
+      </c>
+      <c r="H25" s="33" t="n">
+        <v>46270</v>
       </c>
       <c r="I25" s="30" t="n"/>
       <c r="J25" s="28">
@@ -4036,13 +4006,11 @@
           <t>Audiência de conciliação (confirmar presença do cliente)</t>
         </is>
       </c>
-      <c r="G26" s="33">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
-      </c>
-      <c r="H26" s="33">
-        <f>TODAY()-36</f>
-        <v>46243.0</v>
+      <c r="G26" s="33" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H26" s="33" t="n">
+        <v>46243</v>
       </c>
       <c r="I26" s="30" t="inlineStr">
         <is>
@@ -4101,13 +4069,11 @@
           <t>Juntar documentos enviados pelo cliente</t>
         </is>
       </c>
-      <c r="G27" s="33">
-        <f>TODAY()-6</f>
-        <v>46273.0</v>
-      </c>
-      <c r="H27" s="33">
-        <f>TODAY()-4</f>
-        <v>46275.0</v>
+      <c r="G27" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H27" s="33" t="n">
+        <v>46275</v>
       </c>
       <c r="I27" s="30" t="n"/>
       <c r="J27" s="28">
@@ -4162,13 +4128,11 @@
           <t>Acompanhar a homologação do acordo</t>
         </is>
       </c>
-      <c r="G28" s="33">
-        <f>TODAY()+18</f>
-        <v>46297.0</v>
-      </c>
-      <c r="H28" s="33">
-        <f>TODAY()-33</f>
-        <v>46246.0</v>
+      <c r="G28" s="33" t="n">
+        <v>46297</v>
+      </c>
+      <c r="H28" s="33" t="n">
+        <v>46246</v>
       </c>
       <c r="I28" s="30" t="inlineStr">
         <is>
@@ -4227,13 +4191,11 @@
           <t>Protocolar: contrarrazões</t>
         </is>
       </c>
-      <c r="G29" s="33">
-        <f>TODAY()+27</f>
-        <v>46306.0</v>
-      </c>
-      <c r="H29" s="33">
-        <f>TODAY()-11</f>
-        <v>46268.0</v>
+      <c r="G29" s="33" t="n">
+        <v>46306</v>
+      </c>
+      <c r="H29" s="33" t="n">
+        <v>46268</v>
       </c>
       <c r="I29" s="30" t="n"/>
       <c r="J29" s="28">
@@ -4288,13 +4250,11 @@
           <t>Entregar o parecer ao cliente</t>
         </is>
       </c>
-      <c r="G30" s="33">
-        <f>TODAY()+16</f>
-        <v>46295.0</v>
-      </c>
-      <c r="H30" s="33">
-        <f>TODAY()-15</f>
-        <v>46264.0</v>
+      <c r="G30" s="33" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H30" s="33" t="n">
+        <v>46264</v>
       </c>
       <c r="I30" s="30" t="n"/>
       <c r="J30" s="28">
@@ -4349,13 +4309,11 @@
           <t>Iniciar o cumprimento de sentença</t>
         </is>
       </c>
-      <c r="G31" s="33">
-        <f>TODAY()+22</f>
-        <v>46301.0</v>
-      </c>
-      <c r="H31" s="33">
-        <f>TODAY()-47</f>
-        <v>46232.0</v>
+      <c r="G31" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H31" s="33" t="n">
+        <v>46232</v>
       </c>
       <c r="I31" s="30" t="inlineStr">
         <is>
@@ -4414,13 +4372,11 @@
           <t>Protocolar: réplica</t>
         </is>
       </c>
-      <c r="G32" s="33">
-        <f>TODAY()+1</f>
-        <v>46280.0</v>
-      </c>
-      <c r="H32" s="33">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+      <c r="G32" s="33" t="n">
+        <v>46280</v>
+      </c>
+      <c r="H32" s="33" t="n">
+        <v>46277</v>
       </c>
       <c r="I32" s="30" t="n"/>
       <c r="J32" s="28">
@@ -4475,13 +4431,11 @@
           <t>Protocolar: embargos de declaração</t>
         </is>
       </c>
-      <c r="G33" s="33">
-        <f>TODAY()+3</f>
-        <v>46282.0</v>
-      </c>
-      <c r="H33" s="33">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
+      <c r="G33" s="33" t="n">
+        <v>46282</v>
+      </c>
+      <c r="H33" s="33" t="n">
+        <v>46276</v>
       </c>
       <c r="I33" s="30" t="n"/>
       <c r="J33" s="28">
@@ -4536,13 +4490,11 @@
           <t>Protocolar: manifestação sobre o recurso</t>
         </is>
       </c>
-      <c r="G34" s="33">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
-      </c>
-      <c r="H34" s="33">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+      <c r="G34" s="33" t="n">
+        <v>46278</v>
+      </c>
+      <c r="H34" s="33" t="n">
+        <v>46277</v>
       </c>
       <c r="I34" s="30" t="inlineStr">
         <is>
@@ -13175,16 +13127,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$D$10,0,0,MAX(1,COUNTA(Config!$D$10:$D$19)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$B$10,0,0,MAX(1,COUNTA(Config!$B$10:$B$19)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$10,0,0,MAX(1,COUNTA(Config!$F$10:$F$19)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:H304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="G5:H304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, confira a data de referência (fica em =HOJE()), o número de dias para considerar um caso parado, e as listas de fases, áreas e responsáveis. Preencha de cima para baixo, sem pular linha.</t>
+          <t>Em Config, troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026), o número de dias para considerar um caso parado, e as listas de fases, áreas e responsáveis. Preencha de cima para baixo, sem pular linha.</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>Deixe =HOJE() para acompanhar o dia; troque por uma data para simular outro dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -924,7 +924,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
-        <f>Config!$B$4&amp;" · Andamento dos processos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
+        <f>Config!$B$4&amp;" · Andamento dos processos · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
         <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Andamento dos processos · 14/09/2026</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/02-andamento-por-processo.xlsx
@@ -713,6 +713,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -853,7 +854,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
